--- a/docs/web-experience/13-audio-placement.xlsx
+++ b/docs/web-experience/13-audio-placement.xlsx
@@ -605,19 +605,19 @@
         <v>6.13</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>5.93</v>
+        <v>7.39</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>6.73</v>
+        <v>8.19</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>6.88</v>
+        <v>8.34</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>19.32</v>
+        <v>23.42</v>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
@@ -683,19 +683,19 @@
         <v>10.78</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>4.1</v>
+        <v>5.09</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>7.03</v>
+        <v>8.49</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>11.13</v>
+        <v>13.59</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>11.28</v>
+        <v>13.74</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>19.32</v>
+        <v>23.42</v>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
@@ -761,19 +761,19 @@
         <v>13.68</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2.56</v>
+        <v>3.19</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>11.43</v>
+        <v>13.89</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>13.99</v>
+        <v>17.07</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>14.14</v>
+        <v>17.22</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>19.32</v>
+        <v>23.42</v>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
@@ -839,19 +839,19 @@
         <v>18.14</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>4.08</v>
+        <v>5.09</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>14.29</v>
+        <v>17.37</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>18.37</v>
+        <v>22.47</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>18.52</v>
+        <v>22.62</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>19.32</v>
+        <v>23.42</v>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
@@ -917,16 +917,16 @@
         <v>20.39</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>2.53</v>
+        <v>3</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>2.68</v>
+        <v>3.15</v>
       </c>
       <c r="Q6" s="2" t="n">
         <v>11</v>
@@ -995,16 +995,16 @@
         <v>24.16</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3.24</v>
+        <v>4.02</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>3.84</v>
+        <v>4.62</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>3.99</v>
+        <v>4.77</v>
       </c>
       <c r="Q7" s="2" t="n">
         <v>11</v>
@@ -1073,19 +1073,19 @@
         <v>29.8</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>5.12</v>
+        <v>6.37</v>
       </c>
       <c r="N8" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>5.92</v>
+        <v>7.17</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>6.07</v>
+        <v>7.32</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>6.87</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
@@ -1151,16 +1151,16 @@
         <v>31.71</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="Q9" s="2" t="n">
         <v>11</v>
@@ -1229,19 +1229,19 @@
         <v>5.96</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>5.72</v>
+        <v>7.16</v>
       </c>
       <c r="N10" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>6.52</v>
+        <v>7.96</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>6.67</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>25.6</v>
+        <v>30.85</v>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
@@ -1307,19 +1307,19 @@
         <v>10.62</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>4</v>
+        <v>4.96</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>20.65</v>
+        <v>24.93</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>24.65</v>
+        <v>29.9</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>24.8</v>
+        <v>30.05</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>25.6</v>
+        <v>30.85</v>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
@@ -1385,16 +1385,16 @@
         <v>13.15</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1.85</v>
+        <v>2.32</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>2.45</v>
+        <v>2.92</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>2.6</v>
+        <v>3.07</v>
       </c>
       <c r="Q12" s="2" t="n">
         <v>11</v>
@@ -1463,19 +1463,19 @@
         <v>21.94</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>8.18</v>
+        <v>10.21</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>8.98</v>
+        <v>11.01</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>9.130000000000001</v>
+        <v>11.16</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>20.71</v>
+        <v>25.1</v>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
@@ -1541,19 +1541,19 @@
         <v>26.55</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>3.87</v>
+        <v>4.81</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>15.9</v>
+        <v>19.35</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>19.76</v>
+        <v>24.15</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>19.91</v>
+        <v>24.3</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>20.71</v>
+        <v>25.1</v>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
@@ -1619,19 +1619,19 @@
         <v>29.67</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2.12</v>
+        <v>2.64</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>2.92</v>
+        <v>3.44</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>3.07</v>
+        <v>3.59</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>7.72</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
@@ -1697,19 +1697,19 @@
         <v>33.9</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>3.55</v>
+        <v>4.44</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>3.22</v>
+        <v>3.74</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>6.77</v>
+        <v>8.18</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>6.92</v>
+        <v>8.33</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>7.72</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
@@ -1775,16 +1775,16 @@
         <v>36.21</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1.59</v>
+        <v>1.99</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>2.19</v>
+        <v>2.59</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>2.34</v>
+        <v>2.74</v>
       </c>
       <c r="Q17" s="2" t="n">
         <v>11</v>
@@ -1853,16 +1853,16 @@
         <v>39.95</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3.16</v>
+        <v>3.94</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>3.76</v>
+        <v>4.54</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>3.91</v>
+        <v>4.69</v>
       </c>
       <c r="Q18" s="2" t="n">
         <v>11</v>
@@ -1931,19 +1931,19 @@
         <v>2.5</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>10</v>
+        <v>11.47</v>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
@@ -2009,19 +2009,19 @@
         <v>5.21</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2.19</v>
+        <v>2.72</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>5.54</v>
+        <v>6.61</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>5.69</v>
+        <v>6.76</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>10</v>
+        <v>11.47</v>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
@@ -2087,19 +2087,19 @@
         <v>8.640000000000001</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>5.84</v>
+        <v>6.91</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>8.74</v>
+        <v>10.52</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>8.890000000000001</v>
+        <v>10.67</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>10</v>
+        <v>11.47</v>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
@@ -2165,19 +2165,19 @@
         <v>11.94</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>4.64</v>
+        <v>5.45</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>7.46</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>7.61</v>
+        <v>9.1</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>10.98</v>
+        <v>13.02</v>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
@@ -2243,19 +2243,19 @@
         <v>14.79</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2.27</v>
+        <v>2.82</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>7.76</v>
+        <v>9.25</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>10.03</v>
+        <v>12.07</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>10.18</v>
+        <v>12.22</v>
       </c>
       <c r="Q23" s="2" t="n">
-        <v>10.98</v>
+        <v>13.02</v>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
@@ -2321,19 +2321,19 @@
         <v>20.14</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>4.99</v>
+        <v>6.22</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>5</v>
+        <v>5.89</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>9.99</v>
+        <v>12.11</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>10.14</v>
+        <v>12.26</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>10.94</v>
+        <v>13.06</v>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
@@ -2399,19 +2399,19 @@
         <v>23.88</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>3</v>
+        <v>3.76</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>4.04</v>
+        <v>4.69</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>7.04</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>7.19</v>
+        <v>8.6</v>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
@@ -2477,19 +2477,19 @@
         <v>27.35</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2.93</v>
+        <v>3.66</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>3.36</v>
+        <v>3.86</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>6.28</v>
+        <v>7.51</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>6.43</v>
+        <v>7.66</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>7.23</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
@@ -2555,19 +2555,19 @@
         <v>4.06</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3.84</v>
+        <v>4.78</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>3.18</v>
+        <v>3.59</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>7.02</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>7.17</v>
+        <v>8.52</v>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>8</v>
+        <v>9.32</v>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
@@ -2633,19 +2633,19 @@
         <v>7.63</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>3.16</v>
+        <v>3.92</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>6.81</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>6.96</v>
+        <v>8.26</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>8</v>
+        <v>9.06</v>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
@@ -2711,19 +2711,19 @@
         <v>11.56</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3.27</v>
+        <v>4.05</v>
       </c>
       <c r="N29" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>4.07</v>
+        <v>4.85</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>4.22</v>
+        <v>5</v>
       </c>
       <c r="Q29" s="2" t="n">
-        <v>17.98</v>
+        <v>21.56</v>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
@@ -2789,19 +2789,19 @@
         <v>16.91</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>4.41</v>
+        <v>5.51</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>4.37</v>
+        <v>5.15</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>8.779999999999999</v>
+        <v>10.66</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>8.93</v>
+        <v>10.81</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>17.98</v>
+        <v>21.56</v>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
@@ -2867,19 +2867,19 @@
         <v>21.43</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3.79</v>
+        <v>4.73</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>4.12</v>
+        <v>4.77</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>7.9</v>
+        <v>9.5</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>8.050000000000001</v>
+        <v>9.65</v>
       </c>
       <c r="Q31" s="2" t="n">
-        <v>14.57</v>
+        <v>17.42</v>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
@@ -2945,19 +2945,19 @@
         <v>26.38</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>4.1</v>
+        <v>5.12</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>4.27</v>
+        <v>4.95</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>8.369999999999999</v>
+        <v>10.07</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>8.52</v>
+        <v>10.22</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>14.52</v>
+        <v>17.34</v>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
@@ -3023,19 +3023,19 @@
         <v>31.87</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>4.94</v>
+        <v>6.14</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>4.4</v>
+        <v>5.14</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>9.34</v>
+        <v>11.27</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>9.49</v>
+        <v>11.42</v>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>16.86</v>
+        <v>20.18</v>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
@@ -3101,16 +3101,16 @@
         <v>34.96</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2.46</v>
+        <v>3.06</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>3.23</v>
+        <v>3.67</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>5.68</v>
+        <v>6.73</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>5.83</v>
+        <v>6.88</v>
       </c>
       <c r="Q34" s="2" t="n">
         <v>8</v>
@@ -3179,19 +3179,19 @@
         <v>6.93</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>6.74</v>
+        <v>8.41</v>
       </c>
       <c r="N35" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>7.34</v>
+        <v>9.01</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>7.49</v>
+        <v>9.16</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>8.289999999999999</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
@@ -3257,19 +3257,19 @@
         <v>13.74</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>6.58</v>
+        <v>8.18</v>
       </c>
       <c r="N36" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>7.18</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>7.33</v>
+        <v>8.93</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>8.130000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
@@ -3335,19 +3335,19 @@
         <v>18.43</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>4.36</v>
+        <v>5.43</v>
       </c>
       <c r="N37" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O37" s="2" t="n">
-        <v>4.96</v>
+        <v>6.03</v>
       </c>
       <c r="P37" s="2" t="n">
-        <v>5.11</v>
+        <v>6.18</v>
       </c>
       <c r="Q37" s="2" t="n">
-        <v>5.91</v>
+        <v>6.98</v>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
@@ -3413,19 +3413,19 @@
         <v>24.39</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>5.59</v>
+        <v>6.97</v>
       </c>
       <c r="N38" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>6.19</v>
+        <v>7.57</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>6.34</v>
+        <v>7.72</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>7.14</v>
+        <v>8.52</v>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
@@ -3491,16 +3491,16 @@
         <v>29.23</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>4</v>
+        <v>4.99</v>
       </c>
       <c r="N39" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>4.8</v>
+        <v>5.79</v>
       </c>
       <c r="P39" s="2" t="n">
-        <v>4.95</v>
+        <v>5.94</v>
       </c>
       <c r="Q39" s="2" t="n">
         <v>8</v>
@@ -3569,19 +3569,19 @@
         <v>34.07</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>4.21</v>
+        <v>5.22</v>
       </c>
       <c r="N40" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>4.81</v>
+        <v>5.82</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>4.96</v>
+        <v>5.97</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>5.76</v>
+        <v>6.77</v>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
@@ -3647,19 +3647,19 @@
         <v>38.94</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>4.47</v>
+        <v>5.56</v>
       </c>
       <c r="N41" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>5.27</v>
+        <v>6.36</v>
       </c>
       <c r="P41" s="2" t="n">
-        <v>5.42</v>
+        <v>6.51</v>
       </c>
       <c r="Q41" s="2" t="n">
-        <v>17.27</v>
+        <v>20.95</v>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
@@ -3725,19 +3725,19 @@
         <v>43.71</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>4.55</v>
+        <v>5.67</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>5.57</v>
+        <v>6.66</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>10.11</v>
+        <v>12.33</v>
       </c>
       <c r="P42" s="2" t="n">
-        <v>10.26</v>
+        <v>12.48</v>
       </c>
       <c r="Q42" s="2" t="n">
-        <v>17.27</v>
+        <v>20.95</v>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
@@ -3803,19 +3803,19 @@
         <v>50.32</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>5.9</v>
+        <v>7.37</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>10.41</v>
+        <v>12.63</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>16.32</v>
+        <v>20</v>
       </c>
       <c r="P43" s="2" t="n">
-        <v>16.47</v>
+        <v>20.15</v>
       </c>
       <c r="Q43" s="2" t="n">
-        <v>17.27</v>
+        <v>20.95</v>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
@@ -3881,19 +3881,19 @@
         <v>57.37</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>6.5</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="N44" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>7.3</v>
+        <v>8.92</v>
       </c>
       <c r="P44" s="2" t="n">
-        <v>7.45</v>
+        <v>9.07</v>
       </c>
       <c r="Q44" s="2" t="n">
-        <v>20.84</v>
+        <v>25.23</v>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
@@ -3959,19 +3959,19 @@
         <v>61.81</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>3.94</v>
+        <v>4.91</v>
       </c>
       <c r="N45" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>4.54</v>
+        <v>5.51</v>
       </c>
       <c r="P45" s="2" t="n">
-        <v>4.69</v>
+        <v>5.66</v>
       </c>
       <c r="Q45" s="2" t="n">
-        <v>5.49</v>
+        <v>6.46</v>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
@@ -4037,19 +4037,19 @@
         <v>3.45</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>3.24</v>
+        <v>4.05</v>
       </c>
       <c r="N46" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O46" s="2" t="n">
-        <v>4.04</v>
+        <v>4.85</v>
       </c>
       <c r="P46" s="2" t="n">
-        <v>4.19</v>
+        <v>5</v>
       </c>
       <c r="Q46" s="2" t="n">
-        <v>10.98</v>
+        <v>13.02</v>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
@@ -4115,19 +4115,19 @@
         <v>7.56</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>3.6</v>
+        <v>4.49</v>
       </c>
       <c r="N47" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O47" s="2" t="n">
-        <v>4.4</v>
+        <v>5.29</v>
       </c>
       <c r="P47" s="2" t="n">
-        <v>4.55</v>
+        <v>5.44</v>
       </c>
       <c r="Q47" s="2" t="n">
-        <v>10.94</v>
+        <v>13.06</v>
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
@@ -4193,19 +4193,19 @@
         <v>10.67</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>2.64</v>
+        <v>3.29</v>
       </c>
       <c r="N48" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O48" s="2" t="n">
-        <v>3.44</v>
+        <v>4.09</v>
       </c>
       <c r="P48" s="2" t="n">
-        <v>3.59</v>
+        <v>4.24</v>
       </c>
       <c r="Q48" s="2" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
@@ -4271,19 +4271,19 @@
         <v>13.1</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1.96</v>
+        <v>2.46</v>
       </c>
       <c r="N49" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O49" s="2" t="n">
-        <v>2.76</v>
+        <v>3.26</v>
       </c>
       <c r="P49" s="2" t="n">
-        <v>2.91</v>
+        <v>3.41</v>
       </c>
       <c r="Q49" s="2" t="n">
-        <v>7.23</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
@@ -4349,19 +4349,19 @@
         <v>15.27</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1.78</v>
+        <v>2.19</v>
       </c>
       <c r="N50" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O50" s="2" t="n">
-        <v>2.58</v>
+        <v>2.99</v>
       </c>
       <c r="P50" s="2" t="n">
-        <v>2.73</v>
+        <v>3.14</v>
       </c>
       <c r="Q50" s="2" t="n">
-        <v>8</v>
+        <v>9.32</v>
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
@@ -4427,19 +4427,19 @@
         <v>17.91</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="N51" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O51" s="2" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="P51" s="2" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="Q51" s="2" t="n">
-        <v>8</v>
+        <v>9.06</v>
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
@@ -4505,19 +4505,19 @@
         <v>21.08</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2.72</v>
+        <v>3.37</v>
       </c>
       <c r="N52" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O52" s="2" t="n">
-        <v>3.52</v>
+        <v>4.17</v>
       </c>
       <c r="P52" s="2" t="n">
-        <v>3.67</v>
+        <v>4.32</v>
       </c>
       <c r="Q52" s="2" t="n">
-        <v>14.57</v>
+        <v>17.42</v>
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
@@ -4583,19 +4583,19 @@
         <v>24.37</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2.87</v>
+        <v>3.55</v>
       </c>
       <c r="N53" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O53" s="2" t="n">
-        <v>3.67</v>
+        <v>4.35</v>
       </c>
       <c r="P53" s="2" t="n">
-        <v>3.82</v>
+        <v>4.5</v>
       </c>
       <c r="Q53" s="2" t="n">
-        <v>14.52</v>
+        <v>17.34</v>
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
@@ -4661,19 +4661,19 @@
         <v>27.83</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>3</v>
+        <v>3.74</v>
       </c>
       <c r="N54" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O54" s="2" t="n">
-        <v>3.8</v>
+        <v>4.54</v>
       </c>
       <c r="P54" s="2" t="n">
-        <v>3.95</v>
+        <v>4.69</v>
       </c>
       <c r="Q54" s="2" t="n">
-        <v>16.86</v>
+        <v>20.18</v>
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
@@ -4739,19 +4739,19 @@
         <v>31.22</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>3</v>
+        <v>3.74</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>11.04</v>
+        <v>13.26</v>
       </c>
       <c r="O55" s="2" t="n">
-        <v>14.04</v>
+        <v>16.99</v>
       </c>
       <c r="P55" s="2" t="n">
-        <v>14.19</v>
+        <v>17.14</v>
       </c>
       <c r="Q55" s="2" t="n">
-        <v>25.6</v>
+        <v>30.85</v>
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
@@ -4817,16 +4817,16 @@
         <v>2.05</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1.83</v>
+        <v>2.27</v>
       </c>
       <c r="N56" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O56" s="2" t="n">
-        <v>2.63</v>
+        <v>3.07</v>
       </c>
       <c r="P56" s="2" t="n">
-        <v>2.78</v>
+        <v>3.22</v>
       </c>
       <c r="Q56" s="2" t="n">
         <v>8</v>
@@ -4895,19 +4895,19 @@
         <v>8.68</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>5.8</v>
+        <v>7.26</v>
       </c>
       <c r="N57" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>6.6</v>
+        <v>8.06</v>
       </c>
       <c r="P57" s="2" t="n">
-        <v>6.75</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="Q57" s="2" t="n">
-        <v>17.7</v>
+        <v>21.3</v>
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
@@ -4973,19 +4973,19 @@
         <v>11.17</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1.78</v>
+        <v>2.19</v>
       </c>
       <c r="N58" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O58" s="2" t="n">
-        <v>2.58</v>
+        <v>2.99</v>
       </c>
       <c r="P58" s="2" t="n">
-        <v>2.73</v>
+        <v>3.14</v>
       </c>
       <c r="Q58" s="2" t="n">
-        <v>8</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
@@ -5051,19 +5051,19 @@
         <v>15.72</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3.87</v>
+        <v>4.81</v>
       </c>
       <c r="N59" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O59" s="2" t="n">
-        <v>4.67</v>
+        <v>5.61</v>
       </c>
       <c r="P59" s="2" t="n">
-        <v>4.82</v>
+        <v>5.76</v>
       </c>
       <c r="Q59" s="2" t="n">
-        <v>12.65</v>
+        <v>15.08</v>
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
@@ -5129,19 +5129,19 @@
         <v>18.33</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>2.09</v>
+        <v>2.59</v>
       </c>
       <c r="N60" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O60" s="2" t="n">
-        <v>2.89</v>
+        <v>3.39</v>
       </c>
       <c r="P60" s="2" t="n">
-        <v>3.04</v>
+        <v>3.54</v>
       </c>
       <c r="Q60" s="2" t="n">
-        <v>8</v>
+        <v>9.01</v>
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
@@ -5207,19 +5207,19 @@
         <v>21.68</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>2.77</v>
+        <v>3.42</v>
       </c>
       <c r="N61" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O61" s="2" t="n">
-        <v>3.57</v>
+        <v>4.22</v>
       </c>
       <c r="P61" s="2" t="n">
-        <v>3.72</v>
+        <v>4.37</v>
       </c>
       <c r="Q61" s="2" t="n">
-        <v>8.91</v>
+        <v>10.47</v>
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
@@ -5285,19 +5285,19 @@
         <v>25.71</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>3.34</v>
+        <v>4.15</v>
       </c>
       <c r="N62" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O62" s="2" t="n">
-        <v>4.14</v>
+        <v>4.95</v>
       </c>
       <c r="P62" s="2" t="n">
-        <v>4.29</v>
+        <v>5.1</v>
       </c>
       <c r="Q62" s="2" t="n">
-        <v>8.380000000000001</v>
+        <v>9.85</v>
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
@@ -5363,19 +5363,19 @@
         <v>31.76</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>5.33</v>
+        <v>6.64</v>
       </c>
       <c r="N63" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O63" s="2" t="n">
-        <v>6.13</v>
+        <v>7.44</v>
       </c>
       <c r="P63" s="2" t="n">
-        <v>6.28</v>
+        <v>7.59</v>
       </c>
       <c r="Q63" s="2" t="n">
-        <v>13.18</v>
+        <v>15.74</v>
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
@@ -5441,19 +5441,19 @@
         <v>4.76</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>4.52</v>
+        <v>5.64</v>
       </c>
       <c r="N64" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O64" s="2" t="n">
-        <v>5.32</v>
+        <v>6.44</v>
       </c>
       <c r="P64" s="2" t="n">
-        <v>5.47</v>
+        <v>6.59</v>
       </c>
       <c r="Q64" s="2" t="n">
-        <v>17.53</v>
+        <v>21.29</v>
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
@@ -5519,19 +5519,19 @@
         <v>11.33</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>5.98</v>
+        <v>7.44</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>5.62</v>
+        <v>6.74</v>
       </c>
       <c r="O65" s="2" t="n">
-        <v>11.6</v>
+        <v>14.19</v>
       </c>
       <c r="P65" s="2" t="n">
-        <v>11.75</v>
+        <v>14.34</v>
       </c>
       <c r="Q65" s="2" t="n">
-        <v>17.53</v>
+        <v>21.29</v>
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
@@ -5597,19 +5597,19 @@
         <v>16.53</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>4.68</v>
+        <v>5.85</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>11.9</v>
+        <v>14.49</v>
       </c>
       <c r="O66" s="2" t="n">
-        <v>16.58</v>
+        <v>20.34</v>
       </c>
       <c r="P66" s="2" t="n">
-        <v>16.73</v>
+        <v>20.49</v>
       </c>
       <c r="Q66" s="2" t="n">
-        <v>17.53</v>
+        <v>21.29</v>
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
@@ -5675,19 +5675,19 @@
         <v>20.72</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>3.55</v>
+        <v>4.44</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>4.4</v>
+        <v>5.16</v>
       </c>
       <c r="O67" s="2" t="n">
-        <v>7.96</v>
+        <v>9.6</v>
       </c>
       <c r="P67" s="2" t="n">
-        <v>8.109999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="Q67" s="2" t="n">
-        <v>8.91</v>
+        <v>10.55</v>
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
@@ -5753,19 +5753,19 @@
         <v>24.4</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>3.21</v>
+        <v>4</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>5.27</v>
+        <v>6.21</v>
       </c>
       <c r="O68" s="2" t="n">
-        <v>8.48</v>
+        <v>10.2</v>
       </c>
       <c r="P68" s="2" t="n">
-        <v>8.630000000000001</v>
+        <v>10.35</v>
       </c>
       <c r="Q68" s="2" t="n">
-        <v>12.65</v>
+        <v>15.08</v>
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
@@ -5831,19 +5831,19 @@
         <v>27.72</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2.93</v>
+        <v>3.63</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>8.779999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="O69" s="2" t="n">
-        <v>11.7</v>
+        <v>14.13</v>
       </c>
       <c r="P69" s="2" t="n">
-        <v>11.85</v>
+        <v>14.28</v>
       </c>
       <c r="Q69" s="2" t="n">
-        <v>12.65</v>
+        <v>15.08</v>
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
@@ -5909,19 +5909,19 @@
         <v>31.86</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>3.79</v>
+        <v>4.7</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>4.17</v>
+        <v>4.82</v>
       </c>
       <c r="O70" s="2" t="n">
-        <v>7.96</v>
+        <v>9.52</v>
       </c>
       <c r="P70" s="2" t="n">
-        <v>8.109999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="Q70" s="2" t="n">
-        <v>8.91</v>
+        <v>10.47</v>
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
@@ -5987,19 +5987,19 @@
         <v>34.92</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2.87</v>
+        <v>3.55</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>3.83</v>
+        <v>4.4</v>
       </c>
       <c r="O71" s="2" t="n">
-        <v>6.7</v>
+        <v>7.96</v>
       </c>
       <c r="P71" s="2" t="n">
-        <v>6.85</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="Q71" s="2" t="n">
-        <v>8</v>
+        <v>8.91</v>
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
@@ -6065,19 +6065,19 @@
         <v>37.68</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2.35</v>
+        <v>2.95</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>4.25</v>
+        <v>4.95</v>
       </c>
       <c r="O72" s="2" t="n">
-        <v>6.6</v>
+        <v>7.9</v>
       </c>
       <c r="P72" s="2" t="n">
-        <v>6.75</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Q72" s="2" t="n">
-        <v>8</v>
+        <v>8.85</v>
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
@@ -6143,19 +6143,19 @@
         <v>41.37</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>3.27</v>
+        <v>4.05</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>3.86</v>
+        <v>4.43</v>
       </c>
       <c r="O73" s="2" t="n">
-        <v>7.12</v>
+        <v>8.48</v>
       </c>
       <c r="P73" s="2" t="n">
-        <v>7.27</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="Q73" s="2" t="n">
-        <v>8.07</v>
+        <v>9.43</v>
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
@@ -6221,19 +6221,19 @@
         <v>2.6</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2.4</v>
+        <v>2.98</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>9.380000000000001</v>
+        <v>11.26</v>
       </c>
       <c r="O74" s="2" t="n">
-        <v>11.78</v>
+        <v>14.24</v>
       </c>
       <c r="P74" s="2" t="n">
-        <v>11.93</v>
+        <v>14.39</v>
       </c>
       <c r="Q74" s="2" t="n">
-        <v>17.98</v>
+        <v>21.56</v>
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
@@ -6299,19 +6299,19 @@
         <v>5.53</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2.46</v>
+        <v>3.06</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>12.08</v>
+        <v>14.54</v>
       </c>
       <c r="O75" s="2" t="n">
-        <v>14.54</v>
+        <v>17.6</v>
       </c>
       <c r="P75" s="2" t="n">
-        <v>14.69</v>
+        <v>17.75</v>
       </c>
       <c r="Q75" s="2" t="n">
-        <v>17.98</v>
+        <v>21.56</v>
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
@@ -6377,19 +6377,19 @@
         <v>8.109999999999999</v>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2.19</v>
+        <v>2.72</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>14.84</v>
+        <v>17.9</v>
       </c>
       <c r="O76" s="2" t="n">
-        <v>17.03</v>
+        <v>20.61</v>
       </c>
       <c r="P76" s="2" t="n">
-        <v>17.18</v>
+        <v>20.76</v>
       </c>
       <c r="Q76" s="2" t="n">
-        <v>17.98</v>
+        <v>21.56</v>
       </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
@@ -6455,19 +6455,19 @@
         <v>16.05</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>7.39</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="N77" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O77" s="2" t="n">
-        <v>7.99</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="P77" s="2" t="n">
-        <v>8.140000000000001</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q77" s="2" t="n">
-        <v>8.94</v>
+        <v>10.75</v>
       </c>
       <c r="R77" s="2" t="inlineStr">
         <is>
@@ -6533,19 +6533,19 @@
         <v>21.88</v>
       </c>
       <c r="M78" s="2" t="n">
-        <v>5.12</v>
+        <v>6.37</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>8.5</v>
+        <v>10.1</v>
       </c>
       <c r="O78" s="2" t="n">
-        <v>13.62</v>
+        <v>16.47</v>
       </c>
       <c r="P78" s="2" t="n">
-        <v>13.77</v>
+        <v>16.62</v>
       </c>
       <c r="Q78" s="2" t="n">
-        <v>14.57</v>
+        <v>17.42</v>
       </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
@@ -6611,19 +6611,19 @@
         <v>26.85</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>4.6</v>
+        <v>5.72</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>8.970000000000001</v>
+        <v>10.67</v>
       </c>
       <c r="O79" s="2" t="n">
-        <v>13.57</v>
+        <v>16.39</v>
       </c>
       <c r="P79" s="2" t="n">
-        <v>13.72</v>
+        <v>16.54</v>
       </c>
       <c r="Q79" s="2" t="n">
-        <v>14.52</v>
+        <v>17.34</v>
       </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
@@ -6689,19 +6689,19 @@
         <v>30.35</v>
       </c>
       <c r="M80" s="2" t="n">
-        <v>2.93</v>
+        <v>3.66</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>9.94</v>
+        <v>11.87</v>
       </c>
       <c r="O80" s="2" t="n">
-        <v>12.87</v>
+        <v>15.53</v>
       </c>
       <c r="P80" s="2" t="n">
-        <v>13.02</v>
+        <v>15.68</v>
       </c>
       <c r="Q80" s="2" t="n">
-        <v>16.86</v>
+        <v>20.18</v>
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
@@ -6767,19 +6767,19 @@
         <v>33.39</v>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2.74</v>
+        <v>3.4</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>13.17</v>
+        <v>15.83</v>
       </c>
       <c r="O81" s="2" t="n">
-        <v>15.91</v>
+        <v>19.23</v>
       </c>
       <c r="P81" s="2" t="n">
-        <v>16.06</v>
+        <v>19.38</v>
       </c>
       <c r="Q81" s="2" t="n">
-        <v>16.86</v>
+        <v>20.18</v>
       </c>
       <c r="R81" s="2" t="inlineStr">
         <is>
@@ -6845,19 +6845,19 @@
         <v>3.5</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>3.32</v>
+        <v>4.1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>7.12</v>
+        <v>8.56</v>
       </c>
       <c r="O82" s="2" t="n">
-        <v>10.44</v>
+        <v>12.66</v>
       </c>
       <c r="P82" s="2" t="n">
-        <v>10.59</v>
+        <v>12.81</v>
       </c>
       <c r="Q82" s="2" t="n">
-        <v>25.6</v>
+        <v>30.85</v>
       </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
@@ -6923,19 +6923,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>5.41</v>
+        <v>6.74</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>14.64</v>
+        <v>17.59</v>
       </c>
       <c r="O83" s="2" t="n">
-        <v>20.05</v>
+        <v>24.33</v>
       </c>
       <c r="P83" s="2" t="n">
-        <v>20.2</v>
+        <v>24.48</v>
       </c>
       <c r="Q83" s="2" t="n">
-        <v>25.6</v>
+        <v>30.85</v>
       </c>
       <c r="R83" s="2" t="inlineStr">
         <is>
@@ -7001,19 +7001,19 @@
         <v>13.97</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>3.32</v>
+        <v>4.13</v>
       </c>
       <c r="N84" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O84" s="2" t="n">
-        <v>3.92</v>
+        <v>4.73</v>
       </c>
       <c r="P84" s="2" t="n">
-        <v>4.07</v>
+        <v>4.88</v>
       </c>
       <c r="Q84" s="2" t="n">
-        <v>4.87</v>
+        <v>5.68</v>
       </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
@@ -7079,19 +7079,19 @@
         <v>17.71</v>
       </c>
       <c r="M85" s="2" t="n">
-        <v>3.08</v>
+        <v>3.84</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>10.62</v>
+        <v>12.81</v>
       </c>
       <c r="O85" s="2" t="n">
-        <v>13.7</v>
+        <v>16.65</v>
       </c>
       <c r="P85" s="2" t="n">
-        <v>13.85</v>
+        <v>16.8</v>
       </c>
       <c r="Q85" s="2" t="n">
-        <v>17.7</v>
+        <v>21.3</v>
       </c>
       <c r="R85" s="2" t="inlineStr">
         <is>
@@ -7157,19 +7157,19 @@
         <v>21.01</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2.74</v>
+        <v>3.4</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>14</v>
+        <v>16.95</v>
       </c>
       <c r="O86" s="2" t="n">
-        <v>16.75</v>
+        <v>20.35</v>
       </c>
       <c r="P86" s="2" t="n">
-        <v>16.9</v>
+        <v>20.5</v>
       </c>
       <c r="Q86" s="2" t="n">
-        <v>17.7</v>
+        <v>21.3</v>
       </c>
       <c r="R86" s="2" t="inlineStr">
         <is>
@@ -7235,19 +7235,19 @@
         <v>27.32</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>5.72</v>
+        <v>7.13</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>9.58</v>
+        <v>11.61</v>
       </c>
       <c r="O87" s="2" t="n">
-        <v>15.3</v>
+        <v>18.75</v>
       </c>
       <c r="P87" s="2" t="n">
-        <v>15.45</v>
+        <v>18.9</v>
       </c>
       <c r="Q87" s="2" t="n">
-        <v>20.71</v>
+        <v>25.1</v>
       </c>
       <c r="R87" s="2" t="inlineStr">
         <is>
@@ -7313,19 +7313,19 @@
         <v>31.76</v>
       </c>
       <c r="M88" s="2" t="n">
-        <v>3.89</v>
+        <v>4.83</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>7.9</v>
+        <v>9.52</v>
       </c>
       <c r="O88" s="2" t="n">
-        <v>11.8</v>
+        <v>14.36</v>
       </c>
       <c r="P88" s="2" t="n">
-        <v>11.95</v>
+        <v>14.51</v>
       </c>
       <c r="Q88" s="2" t="n">
-        <v>20.84</v>
+        <v>25.23</v>
       </c>
       <c r="R88" s="2" t="inlineStr">
         <is>
@@ -7391,19 +7391,19 @@
         <v>3.12</v>
       </c>
       <c r="M89" s="2" t="n">
-        <v>2.82</v>
+        <v>3.55</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>7.2</v>
+        <v>8.66</v>
       </c>
       <c r="O89" s="2" t="n">
-        <v>10.02</v>
+        <v>12.21</v>
       </c>
       <c r="P89" s="2" t="n">
-        <v>10.17</v>
+        <v>12.36</v>
       </c>
       <c r="Q89" s="2" t="n">
-        <v>17.7</v>
+        <v>21.3</v>
       </c>
       <c r="R89" s="2" t="inlineStr">
         <is>
@@ -7469,19 +7469,19 @@
         <v>6.79</v>
       </c>
       <c r="M90" s="2" t="n">
-        <v>3.08</v>
+        <v>3.81</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>3.18</v>
+        <v>3.59</v>
       </c>
       <c r="O90" s="2" t="n">
-        <v>6.26</v>
+        <v>7.41</v>
       </c>
       <c r="P90" s="2" t="n">
-        <v>6.41</v>
+        <v>7.56</v>
       </c>
       <c r="Q90" s="2" t="n">
-        <v>8</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="R90" s="2" t="inlineStr">
         <is>
@@ -7547,19 +7547,19 @@
         <v>10.43</v>
       </c>
       <c r="M91" s="2" t="n">
-        <v>3</v>
+        <v>3.76</v>
       </c>
       <c r="N91" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O91" s="2" t="n">
-        <v>3.8</v>
+        <v>4.56</v>
       </c>
       <c r="P91" s="2" t="n">
-        <v>3.95</v>
+        <v>4.71</v>
       </c>
       <c r="Q91" s="2" t="n">
-        <v>8.91</v>
+        <v>10.55</v>
       </c>
       <c r="R91" s="2" t="inlineStr">
         <is>
@@ -7625,19 +7625,19 @@
         <v>14.4</v>
       </c>
       <c r="M92" s="2" t="n">
-        <v>3.27</v>
+        <v>4.08</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>3.49</v>
+        <v>3.99</v>
       </c>
       <c r="O92" s="2" t="n">
-        <v>6.76</v>
+        <v>8.06</v>
       </c>
       <c r="P92" s="2" t="n">
-        <v>6.91</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="Q92" s="2" t="n">
-        <v>8</v>
+        <v>9.01</v>
       </c>
       <c r="R92" s="2" t="inlineStr">
         <is>
@@ -7703,19 +7703,19 @@
         <v>17.76</v>
       </c>
       <c r="M93" s="2" t="n">
-        <v>2.69</v>
+        <v>3.34</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>4.74</v>
+        <v>5.55</v>
       </c>
       <c r="O93" s="2" t="n">
-        <v>7.43</v>
+        <v>8.9</v>
       </c>
       <c r="P93" s="2" t="n">
-        <v>7.58</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="Q93" s="2" t="n">
-        <v>8.380000000000001</v>
+        <v>9.85</v>
       </c>
       <c r="R93" s="2" t="inlineStr">
         <is>
@@ -7781,19 +7781,19 @@
         <v>19.35</v>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>6.73</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="O94" s="2" t="n">
-        <v>7.75</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="P94" s="2" t="n">
-        <v>7.9</v>
+        <v>9.44</v>
       </c>
       <c r="Q94" s="2" t="n">
-        <v>13.18</v>
+        <v>15.74</v>
       </c>
       <c r="R94" s="2" t="inlineStr">
         <is>
@@ -7859,19 +7859,19 @@
         <v>24.08</v>
       </c>
       <c r="M95" s="2" t="n">
-        <v>4.18</v>
+        <v>5.2</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>8.050000000000001</v>
+        <v>9.59</v>
       </c>
       <c r="O95" s="2" t="n">
-        <v>12.23</v>
+        <v>14.79</v>
       </c>
       <c r="P95" s="2" t="n">
-        <v>12.38</v>
+        <v>14.94</v>
       </c>
       <c r="Q95" s="2" t="n">
-        <v>13.18</v>
+        <v>15.74</v>
       </c>
       <c r="R95" s="2" t="inlineStr">
         <is>
@@ -7937,19 +7937,19 @@
         <v>28.77</v>
       </c>
       <c r="M96" s="2" t="n">
-        <v>4.13</v>
+        <v>5.15</v>
       </c>
       <c r="N96" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O96" s="2" t="n">
-        <v>4.93</v>
+        <v>5.95</v>
       </c>
       <c r="P96" s="2" t="n">
-        <v>5.08</v>
+        <v>6.1</v>
       </c>
       <c r="Q96" s="2" t="n">
-        <v>15.48</v>
+        <v>18.64</v>
       </c>
       <c r="R96" s="2" t="inlineStr">
         <is>
@@ -8015,19 +8015,19 @@
         <v>32.92</v>
       </c>
       <c r="M97" s="2" t="n">
-        <v>3.63</v>
+        <v>4.52</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>4.74</v>
+        <v>5.55</v>
       </c>
       <c r="O97" s="2" t="n">
-        <v>8.369999999999999</v>
+        <v>10.07</v>
       </c>
       <c r="P97" s="2" t="n">
-        <v>8.52</v>
+        <v>10.22</v>
       </c>
       <c r="Q97" s="2" t="n">
-        <v>9.32</v>
+        <v>11.02</v>
       </c>
       <c r="R97" s="2" t="inlineStr">
         <is>
@@ -8093,19 +8093,19 @@
         <v>37.77</v>
       </c>
       <c r="M98" s="2" t="n">
-        <v>4.31</v>
+        <v>5.36</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>5.95</v>
+        <v>7.04</v>
       </c>
       <c r="O98" s="2" t="n">
-        <v>10.26</v>
+        <v>12.4</v>
       </c>
       <c r="P98" s="2" t="n">
-        <v>10.41</v>
+        <v>12.55</v>
       </c>
       <c r="Q98" s="2" t="n">
-        <v>11.21</v>
+        <v>13.35</v>
       </c>
       <c r="R98" s="2" t="inlineStr">
         <is>
@@ -8171,19 +8171,19 @@
         <v>41.65</v>
       </c>
       <c r="M99" s="2" t="n">
-        <v>3.32</v>
+        <v>4.13</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>4.38</v>
+        <v>5.08</v>
       </c>
       <c r="O99" s="2" t="n">
-        <v>7.7</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="P99" s="2" t="n">
-        <v>7.85</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="Q99" s="2" t="n">
-        <v>8.65</v>
+        <v>10.16</v>
       </c>
       <c r="R99" s="2" t="inlineStr">
         <is>
@@ -8249,19 +8249,19 @@
         <v>45.15</v>
       </c>
       <c r="M100" s="2" t="n">
-        <v>2.93</v>
+        <v>3.66</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>6.42</v>
+        <v>7.64</v>
       </c>
       <c r="O100" s="2" t="n">
-        <v>9.34</v>
+        <v>11.3</v>
       </c>
       <c r="P100" s="2" t="n">
-        <v>9.49</v>
+        <v>11.45</v>
       </c>
       <c r="Q100" s="2" t="n">
-        <v>12.03</v>
+        <v>14.33</v>
       </c>
       <c r="R100" s="2" t="inlineStr">
         <is>
@@ -8327,19 +8327,19 @@
         <v>47.08</v>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1.44</v>
+        <v>1.78</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>9.640000000000001</v>
+        <v>11.6</v>
       </c>
       <c r="O101" s="2" t="n">
-        <v>11.08</v>
+        <v>13.38</v>
       </c>
       <c r="P101" s="2" t="n">
-        <v>11.23</v>
+        <v>13.53</v>
       </c>
       <c r="Q101" s="2" t="n">
-        <v>12.03</v>
+        <v>14.33</v>
       </c>
       <c r="R101" s="2" t="inlineStr">
         <is>
@@ -8405,19 +8405,19 @@
         <v>50.22</v>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2.64</v>
+        <v>3.27</v>
       </c>
       <c r="N102" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O102" s="2" t="n">
-        <v>3.44</v>
+        <v>4.07</v>
       </c>
       <c r="P102" s="2" t="n">
-        <v>3.59</v>
+        <v>4.22</v>
       </c>
       <c r="Q102" s="2" t="n">
-        <v>12.76</v>
+        <v>15.21</v>
       </c>
       <c r="R102" s="2" t="inlineStr">
         <is>
@@ -8483,19 +8483,19 @@
         <v>54.17</v>
       </c>
       <c r="M103" s="2" t="n">
-        <v>3.37</v>
+        <v>4.21</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>3.74</v>
+        <v>4.37</v>
       </c>
       <c r="O103" s="2" t="n">
-        <v>7.11</v>
+        <v>8.57</v>
       </c>
       <c r="P103" s="2" t="n">
-        <v>7.26</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="Q103" s="2" t="n">
-        <v>12.76</v>
+        <v>15.21</v>
       </c>
       <c r="R103" s="2" t="inlineStr">
         <is>
@@ -8561,19 +8561,19 @@
         <v>2.6</v>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="N104" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O104" s="2" t="n">
-        <v>3.23</v>
+        <v>3.8</v>
       </c>
       <c r="P104" s="2" t="n">
-        <v>3.38</v>
+        <v>3.95</v>
       </c>
       <c r="Q104" s="2" t="n">
-        <v>8</v>
+        <v>8.91</v>
       </c>
       <c r="R104" s="2" t="inlineStr">
         <is>
@@ -8639,19 +8639,19 @@
         <v>6.63</v>
       </c>
       <c r="M105" s="2" t="n">
-        <v>3.34</v>
+        <v>4.15</v>
       </c>
       <c r="N105" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O105" s="2" t="n">
-        <v>4.14</v>
+        <v>4.95</v>
       </c>
       <c r="P105" s="2" t="n">
-        <v>4.29</v>
+        <v>5.1</v>
       </c>
       <c r="Q105" s="2" t="n">
-        <v>9.32</v>
+        <v>11.02</v>
       </c>
       <c r="R105" s="2" t="inlineStr">
         <is>
@@ -8717,19 +8717,19 @@
         <v>12.02</v>
       </c>
       <c r="M106" s="2" t="n">
-        <v>4.55</v>
+        <v>5.64</v>
       </c>
       <c r="N106" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O106" s="2" t="n">
-        <v>5.35</v>
+        <v>6.44</v>
       </c>
       <c r="P106" s="2" t="n">
-        <v>5.5</v>
+        <v>6.59</v>
       </c>
       <c r="Q106" s="2" t="n">
-        <v>11.21</v>
+        <v>13.35</v>
       </c>
       <c r="R106" s="2" t="inlineStr">
         <is>
@@ -8795,19 +8795,19 @@
         <v>15.51</v>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2.85</v>
+        <v>3.55</v>
       </c>
       <c r="N107" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O107" s="2" t="n">
-        <v>3.65</v>
+        <v>4.35</v>
       </c>
       <c r="P107" s="2" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="Q107" s="2" t="n">
-        <v>8</v>
+        <v>8.85</v>
       </c>
       <c r="R107" s="2" t="inlineStr">
         <is>
@@ -8873,19 +8873,19 @@
         <v>19.24</v>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2.98</v>
+        <v>3.68</v>
       </c>
       <c r="N108" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O108" s="2" t="n">
-        <v>3.78</v>
+        <v>4.48</v>
       </c>
       <c r="P108" s="2" t="n">
-        <v>3.93</v>
+        <v>4.63</v>
       </c>
       <c r="Q108" s="2" t="n">
-        <v>8.65</v>
+        <v>10.16</v>
       </c>
       <c r="R108" s="2" t="inlineStr">
         <is>
@@ -8951,19 +8951,19 @@
         <v>24.95</v>
       </c>
       <c r="M109" s="2" t="n">
-        <v>5.02</v>
+        <v>6.24</v>
       </c>
       <c r="N109" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O109" s="2" t="n">
-        <v>5.82</v>
+        <v>7.04</v>
       </c>
       <c r="P109" s="2" t="n">
-        <v>5.97</v>
+        <v>7.19</v>
       </c>
       <c r="Q109" s="2" t="n">
-        <v>12.03</v>
+        <v>14.33</v>
       </c>
       <c r="R109" s="2" t="inlineStr">
         <is>
@@ -9029,19 +9029,19 @@
         <v>28.05</v>
       </c>
       <c r="M110" s="2" t="n">
-        <v>2.46</v>
+        <v>3.03</v>
       </c>
       <c r="N110" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O110" s="2" t="n">
-        <v>3.26</v>
+        <v>3.83</v>
       </c>
       <c r="P110" s="2" t="n">
-        <v>3.41</v>
+        <v>3.98</v>
       </c>
       <c r="Q110" s="2" t="n">
-        <v>8.07</v>
+        <v>9.43</v>
       </c>
       <c r="R110" s="2" t="inlineStr">
         <is>
@@ -9107,19 +9107,19 @@
         <v>5.7</v>
       </c>
       <c r="M111" s="2" t="n">
-        <v>5.46</v>
+        <v>6.82</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>5.53</v>
+        <v>6.55</v>
       </c>
       <c r="O111" s="2" t="n">
-        <v>10.99</v>
+        <v>13.36</v>
       </c>
       <c r="P111" s="2" t="n">
-        <v>11.14</v>
+        <v>13.51</v>
       </c>
       <c r="Q111" s="2" t="n">
-        <v>15.48</v>
+        <v>18.64</v>
       </c>
       <c r="R111" s="2" t="inlineStr">
         <is>
@@ -9185,19 +9185,19 @@
         <v>9.19</v>
       </c>
       <c r="M112" s="2" t="n">
-        <v>3.24</v>
+        <v>4.02</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>11.29</v>
+        <v>13.66</v>
       </c>
       <c r="O112" s="2" t="n">
-        <v>14.53</v>
+        <v>17.69</v>
       </c>
       <c r="P112" s="2" t="n">
-        <v>14.68</v>
+        <v>17.84</v>
       </c>
       <c r="Q112" s="2" t="n">
-        <v>15.48</v>
+        <v>18.64</v>
       </c>
       <c r="R112" s="2" t="inlineStr">
         <is>
@@ -9263,19 +9263,19 @@
         <v>11.89</v>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2.12</v>
+        <v>2.61</v>
       </c>
       <c r="N113" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O113" s="2" t="n">
-        <v>2.92</v>
+        <v>3.41</v>
       </c>
       <c r="P113" s="2" t="n">
-        <v>3.07</v>
+        <v>3.56</v>
       </c>
       <c r="Q113" s="2" t="n">
-        <v>7.43</v>
+        <v>8.74</v>
       </c>
       <c r="R113" s="2" t="inlineStr">
         <is>
@@ -9341,19 +9341,19 @@
         <v>15.39</v>
       </c>
       <c r="M114" s="2" t="n">
-        <v>3.27</v>
+        <v>4.08</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>3.22</v>
+        <v>3.71</v>
       </c>
       <c r="O114" s="2" t="n">
-        <v>6.48</v>
+        <v>7.79</v>
       </c>
       <c r="P114" s="2" t="n">
-        <v>6.63</v>
+        <v>7.94</v>
       </c>
       <c r="Q114" s="2" t="n">
-        <v>7.43</v>
+        <v>8.74</v>
       </c>
       <c r="R114" s="2" t="inlineStr">
         <is>
@@ -9419,16 +9419,16 @@
         <v>19.59</v>
       </c>
       <c r="M115" s="2" t="n">
-        <v>3.24</v>
+        <v>4.02</v>
       </c>
       <c r="N115" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O115" s="2" t="n">
-        <v>3.84</v>
+        <v>4.62</v>
       </c>
       <c r="P115" s="2" t="n">
-        <v>3.99</v>
+        <v>4.77</v>
       </c>
       <c r="Q115" s="2" t="n">
         <v>11</v>
@@ -9497,19 +9497,19 @@
         <v>24.07</v>
       </c>
       <c r="M116" s="2" t="n">
-        <v>3.81</v>
+        <v>4.75</v>
       </c>
       <c r="N116" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O116" s="2" t="n">
-        <v>4.61</v>
+        <v>5.55</v>
       </c>
       <c r="P116" s="2" t="n">
-        <v>4.76</v>
+        <v>5.7</v>
       </c>
       <c r="Q116" s="2" t="n">
-        <v>15.62</v>
+        <v>18.86</v>
       </c>
       <c r="R116" s="2" t="inlineStr">
         <is>
@@ -9575,19 +9575,19 @@
         <v>29.56</v>
       </c>
       <c r="M117" s="2" t="n">
-        <v>5.46</v>
+        <v>6.79</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>4.91</v>
+        <v>5.85</v>
       </c>
       <c r="O117" s="2" t="n">
-        <v>10.37</v>
+        <v>12.65</v>
       </c>
       <c r="P117" s="2" t="n">
-        <v>10.52</v>
+        <v>12.8</v>
       </c>
       <c r="Q117" s="2" t="n">
-        <v>15.62</v>
+        <v>18.86</v>
       </c>
       <c r="R117" s="2" t="inlineStr">
         <is>
@@ -9653,19 +9653,19 @@
         <v>33.6</v>
       </c>
       <c r="M118" s="2" t="n">
-        <v>4</v>
+        <v>4.96</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>10.67</v>
+        <v>12.95</v>
       </c>
       <c r="O118" s="2" t="n">
-        <v>14.67</v>
+        <v>17.91</v>
       </c>
       <c r="P118" s="2" t="n">
-        <v>14.82</v>
+        <v>18.06</v>
       </c>
       <c r="Q118" s="2" t="n">
-        <v>15.62</v>
+        <v>18.86</v>
       </c>
       <c r="R118" s="2" t="inlineStr">
         <is>
@@ -9731,19 +9731,19 @@
         <v>38.05</v>
       </c>
       <c r="M119" s="2" t="n">
-        <v>4.18</v>
+        <v>5.2</v>
       </c>
       <c r="N119" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O119" s="2" t="n">
-        <v>4.78</v>
+        <v>5.8</v>
       </c>
       <c r="P119" s="2" t="n">
-        <v>4.93</v>
+        <v>5.95</v>
       </c>
       <c r="Q119" s="2" t="n">
-        <v>11</v>
+        <v>11.75</v>
       </c>
       <c r="R119" s="2" t="inlineStr">
         <is>
@@ -9809,19 +9809,19 @@
         <v>3.43</v>
       </c>
       <c r="M120" s="2" t="n">
-        <v>3.27</v>
+        <v>4.05</v>
       </c>
       <c r="N120" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O120" s="2" t="n">
-        <v>4.07</v>
+        <v>4.85</v>
       </c>
       <c r="P120" s="2" t="n">
-        <v>4.22</v>
+        <v>5</v>
       </c>
       <c r="Q120" s="2" t="n">
-        <v>18.89</v>
+        <v>22.99</v>
       </c>
       <c r="R120" s="2" t="inlineStr">
         <is>
@@ -9887,19 +9887,19 @@
         <v>12.39</v>
       </c>
       <c r="M121" s="2" t="n">
-        <v>8.33</v>
+        <v>10.42</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>4.37</v>
+        <v>5.15</v>
       </c>
       <c r="O121" s="2" t="n">
-        <v>12.7</v>
+        <v>15.57</v>
       </c>
       <c r="P121" s="2" t="n">
-        <v>12.85</v>
+        <v>15.72</v>
       </c>
       <c r="Q121" s="2" t="n">
-        <v>18.89</v>
+        <v>22.99</v>
       </c>
       <c r="R121" s="2" t="inlineStr">
         <is>
@@ -9965,19 +9965,19 @@
         <v>18.2</v>
       </c>
       <c r="M122" s="2" t="n">
-        <v>4.94</v>
+        <v>6.16</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>13</v>
+        <v>15.87</v>
       </c>
       <c r="O122" s="2" t="n">
-        <v>17.94</v>
+        <v>22.04</v>
       </c>
       <c r="P122" s="2" t="n">
-        <v>18.09</v>
+        <v>22.19</v>
       </c>
       <c r="Q122" s="2" t="n">
-        <v>18.89</v>
+        <v>22.99</v>
       </c>
       <c r="R122" s="2" t="inlineStr">
         <is>
@@ -10043,19 +10043,19 @@
         <v>23.17</v>
       </c>
       <c r="M123" s="2" t="n">
-        <v>4.1</v>
+        <v>5.09</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>7.71</v>
+        <v>9.17</v>
       </c>
       <c r="O123" s="2" t="n">
-        <v>11.81</v>
+        <v>14.26</v>
       </c>
       <c r="P123" s="2" t="n">
-        <v>11.96</v>
+        <v>14.41</v>
       </c>
       <c r="Q123" s="2" t="n">
-        <v>12.76</v>
+        <v>15.21</v>
       </c>
       <c r="R123" s="2" t="inlineStr">
         <is>
@@ -10121,19 +10121,19 @@
         <v>29.04</v>
       </c>
       <c r="M124" s="2" t="n">
-        <v>5.07</v>
+        <v>6.32</v>
       </c>
       <c r="N124" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O124" s="2" t="n">
-        <v>5.87</v>
+        <v>7.12</v>
       </c>
       <c r="P124" s="2" t="n">
-        <v>6.02</v>
+        <v>7.27</v>
       </c>
       <c r="Q124" s="2" t="n">
-        <v>6.82</v>
+        <v>8.07</v>
       </c>
       <c r="R124" s="2" t="inlineStr">
         <is>
@@ -10199,19 +10199,19 @@
         <v>31.81</v>
       </c>
       <c r="M125" s="2" t="n">
-        <v>2.06</v>
+        <v>2.59</v>
       </c>
       <c r="N125" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O125" s="2" t="n">
-        <v>2.66</v>
+        <v>3.19</v>
       </c>
       <c r="P125" s="2" t="n">
-        <v>2.81</v>
+        <v>3.34</v>
       </c>
       <c r="Q125" s="2" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="R125" s="2" t="inlineStr">
         <is>
@@ -10277,19 +10277,19 @@
         <v>35.63</v>
       </c>
       <c r="M126" s="2" t="n">
-        <v>3.24</v>
+        <v>4.05</v>
       </c>
       <c r="N126" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O126" s="2" t="n">
-        <v>3.84</v>
+        <v>4.65</v>
       </c>
       <c r="P126" s="2" t="n">
-        <v>3.99</v>
+        <v>4.8</v>
       </c>
       <c r="Q126" s="2" t="n">
-        <v>4.79</v>
+        <v>5.6</v>
       </c>
       <c r="R126" s="2" t="inlineStr">
         <is>
@@ -10355,19 +10355,19 @@
         <v>2.66</v>
       </c>
       <c r="M127" s="2" t="n">
-        <v>2.48</v>
+        <v>3.06</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>12.1</v>
+        <v>14.66</v>
       </c>
       <c r="O127" s="2" t="n">
-        <v>14.58</v>
+        <v>17.71</v>
       </c>
       <c r="P127" s="2" t="n">
-        <v>14.73</v>
+        <v>17.86</v>
       </c>
       <c r="Q127" s="2" t="n">
-        <v>20.84</v>
+        <v>25.23</v>
       </c>
       <c r="R127" s="2" t="inlineStr">
         <is>
@@ -10433,19 +10433,19 @@
         <v>8</v>
       </c>
       <c r="M128" s="2" t="n">
-        <v>5.02</v>
+        <v>6.27</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>14.88</v>
+        <v>18.01</v>
       </c>
       <c r="O128" s="2" t="n">
-        <v>19.89</v>
+        <v>24.28</v>
       </c>
       <c r="P128" s="2" t="n">
-        <v>20.04</v>
+        <v>24.43</v>
       </c>
       <c r="Q128" s="2" t="n">
-        <v>20.84</v>
+        <v>25.23</v>
       </c>
       <c r="R128" s="2" t="inlineStr">
         <is>
@@ -10511,19 +10511,19 @@
         <v>12.43</v>
       </c>
       <c r="M129" s="2" t="n">
-        <v>3.92</v>
+        <v>4.88</v>
       </c>
       <c r="N129" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O129" s="2" t="n">
-        <v>4.72</v>
+        <v>5.68</v>
       </c>
       <c r="P129" s="2" t="n">
-        <v>4.87</v>
+        <v>5.83</v>
       </c>
       <c r="Q129" s="2" t="n">
-        <v>21.41</v>
+        <v>26.06</v>
       </c>
       <c r="R129" s="2" t="inlineStr">
         <is>
@@ -10589,19 +10589,19 @@
         <v>17.72</v>
       </c>
       <c r="M130" s="2" t="n">
-        <v>4.91</v>
+        <v>6.14</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>5.02</v>
+        <v>5.98</v>
       </c>
       <c r="O130" s="2" t="n">
-        <v>9.93</v>
+        <v>12.12</v>
       </c>
       <c r="P130" s="2" t="n">
-        <v>10.08</v>
+        <v>12.27</v>
       </c>
       <c r="Q130" s="2" t="n">
-        <v>21.41</v>
+        <v>26.06</v>
       </c>
       <c r="R130" s="2" t="inlineStr">
         <is>
@@ -10667,19 +10667,19 @@
         <v>21.57</v>
       </c>
       <c r="M131" s="2" t="n">
-        <v>3.47</v>
+        <v>4.34</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>10.23</v>
+        <v>12.42</v>
       </c>
       <c r="O131" s="2" t="n">
-        <v>13.7</v>
+        <v>16.76</v>
       </c>
       <c r="P131" s="2" t="n">
-        <v>13.85</v>
+        <v>16.91</v>
       </c>
       <c r="Q131" s="2" t="n">
-        <v>21.41</v>
+        <v>26.06</v>
       </c>
       <c r="R131" s="2" t="inlineStr">
         <is>
@@ -10745,19 +10745,19 @@
         <v>28.42</v>
       </c>
       <c r="M132" s="2" t="n">
-        <v>6.45</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>14</v>
+        <v>17.06</v>
       </c>
       <c r="O132" s="2" t="n">
-        <v>20.46</v>
+        <v>25.11</v>
       </c>
       <c r="P132" s="2" t="n">
-        <v>20.61</v>
+        <v>25.26</v>
       </c>
       <c r="Q132" s="2" t="n">
-        <v>21.41</v>
+        <v>26.06</v>
       </c>
       <c r="R132" s="2" t="inlineStr">
         <is>
@@ -10823,19 +10823,19 @@
         <v>2.78</v>
       </c>
       <c r="M133" s="2" t="n">
-        <v>2.56</v>
+        <v>3.16</v>
       </c>
       <c r="N133" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O133" s="2" t="n">
-        <v>3.16</v>
+        <v>3.76</v>
       </c>
       <c r="P133" s="2" t="n">
-        <v>3.31</v>
+        <v>3.91</v>
       </c>
       <c r="Q133" s="2" t="n">
-        <v>4.11</v>
+        <v>4.71</v>
       </c>
       <c r="R133" s="2" t="inlineStr">
         <is>
@@ -10901,19 +10901,19 @@
         <v>6.11</v>
       </c>
       <c r="M134" s="2" t="n">
-        <v>2.64</v>
+        <v>3.29</v>
       </c>
       <c r="N134" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O134" s="2" t="n">
-        <v>3.24</v>
+        <v>3.89</v>
       </c>
       <c r="P134" s="2" t="n">
-        <v>3.39</v>
+        <v>4.04</v>
       </c>
       <c r="Q134" s="2" t="n">
-        <v>4.19</v>
+        <v>4.84</v>
       </c>
       <c r="R134" s="2" t="inlineStr">
         <is>
@@ -10979,19 +10979,19 @@
         <v>10.61</v>
       </c>
       <c r="M135" s="2" t="n">
-        <v>3.13</v>
+        <v>3.92</v>
       </c>
       <c r="N135" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O135" s="2" t="n">
-        <v>3.93</v>
+        <v>4.72</v>
       </c>
       <c r="P135" s="2" t="n">
-        <v>4.08</v>
+        <v>4.87</v>
       </c>
       <c r="Q135" s="2" t="n">
-        <v>18.32</v>
+        <v>22.19</v>
       </c>
       <c r="R135" s="2" t="inlineStr">
         <is>
@@ -11057,19 +11057,19 @@
         <v>16.76</v>
       </c>
       <c r="M136" s="2" t="n">
-        <v>5.56</v>
+        <v>6.95</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>4.23</v>
+        <v>5.02</v>
       </c>
       <c r="O136" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>11.97</v>
       </c>
       <c r="P136" s="2" t="n">
-        <v>9.949999999999999</v>
+        <v>12.12</v>
       </c>
       <c r="Q136" s="2" t="n">
-        <v>18.32</v>
+        <v>22.19</v>
       </c>
       <c r="R136" s="2" t="inlineStr">
         <is>
@@ -11135,19 +11135,19 @@
         <v>20.59</v>
       </c>
       <c r="M137" s="2" t="n">
-        <v>3.21</v>
+        <v>4</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>10.1</v>
+        <v>12.27</v>
       </c>
       <c r="O137" s="2" t="n">
-        <v>13.31</v>
+        <v>16.26</v>
       </c>
       <c r="P137" s="2" t="n">
-        <v>13.46</v>
+        <v>16.41</v>
       </c>
       <c r="Q137" s="2" t="n">
-        <v>18.32</v>
+        <v>22.19</v>
       </c>
       <c r="R137" s="2" t="inlineStr">
         <is>
@@ -11213,19 +11213,19 @@
         <v>24.79</v>
       </c>
       <c r="M138" s="2" t="n">
-        <v>3.76</v>
+        <v>4.68</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>13.61</v>
+        <v>16.56</v>
       </c>
       <c r="O138" s="2" t="n">
-        <v>17.37</v>
+        <v>21.24</v>
       </c>
       <c r="P138" s="2" t="n">
-        <v>17.52</v>
+        <v>21.39</v>
       </c>
       <c r="Q138" s="2" t="n">
-        <v>18.32</v>
+        <v>22.19</v>
       </c>
       <c r="R138" s="2" t="inlineStr">
         <is>

--- a/docs/web-experience/13-audio-placement.xlsx
+++ b/docs/web-experience/13-audio-placement.xlsx
@@ -605,19 +605,19 @@
         <v>6.13</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>7.39</v>
+        <v>5.93</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>8.19</v>
+        <v>6.73</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>8.34</v>
+        <v>6.88</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>23.42</v>
+        <v>20.32</v>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
@@ -683,19 +683,19 @@
         <v>10.78</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>5.09</v>
+        <v>4.1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>8.49</v>
+        <v>7.03</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>13.59</v>
+        <v>11.13</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>13.74</v>
+        <v>11.28</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>23.42</v>
+        <v>20.32</v>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
@@ -761,19 +761,19 @@
         <v>13.68</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3.19</v>
+        <v>2.56</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>13.89</v>
+        <v>11.43</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>17.07</v>
+        <v>13.99</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>17.22</v>
+        <v>14.14</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>23.42</v>
+        <v>20.32</v>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
@@ -839,19 +839,19 @@
         <v>18.14</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>5.09</v>
+        <v>4.08</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>17.37</v>
+        <v>14.29</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>22.47</v>
+        <v>18.37</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>22.62</v>
+        <v>18.52</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>23.42</v>
+        <v>20.32</v>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
@@ -917,19 +917,19 @@
         <v>20.39</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>3</v>
+        <v>2.53</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>3.15</v>
+        <v>2.68</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>11</v>
+        <v>16.82</v>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
@@ -995,19 +995,19 @@
         <v>24.16</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>4.02</v>
+        <v>3.24</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>4.62</v>
+        <v>3.84</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>4.77</v>
+        <v>3.99</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>11</v>
+        <v>17.97</v>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
@@ -1073,19 +1073,19 @@
         <v>29.8</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>6.37</v>
+        <v>5.12</v>
       </c>
       <c r="N8" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>7.17</v>
+        <v>5.92</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>7.32</v>
+        <v>6.07</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>8.119999999999999</v>
+        <v>7.87</v>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
@@ -1151,19 +1151,19 @@
         <v>31.71</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
@@ -1229,19 +1229,19 @@
         <v>5.96</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>7.16</v>
+        <v>5.72</v>
       </c>
       <c r="N10" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>7.96</v>
+        <v>6.52</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>8.109999999999999</v>
+        <v>6.67</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>30.85</v>
+        <v>26.6</v>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
@@ -1307,19 +1307,19 @@
         <v>10.62</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>4.96</v>
+        <v>4</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>24.93</v>
+        <v>20.65</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>29.9</v>
+        <v>24.65</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>30.05</v>
+        <v>24.8</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>30.85</v>
+        <v>26.6</v>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
@@ -1385,19 +1385,19 @@
         <v>13.15</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2.32</v>
+        <v>1.85</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>2.92</v>
+        <v>2.45</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>3.07</v>
+        <v>2.6</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>11</v>
+        <v>13.32</v>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
@@ -1463,19 +1463,19 @@
         <v>21.94</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>10.21</v>
+        <v>8.18</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>11.01</v>
+        <v>8.98</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>11.16</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>25.1</v>
+        <v>21.71</v>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
@@ -1541,19 +1541,19 @@
         <v>26.55</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>4.81</v>
+        <v>3.87</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>19.35</v>
+        <v>15.9</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>24.15</v>
+        <v>19.76</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>24.3</v>
+        <v>19.91</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>25.1</v>
+        <v>21.71</v>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
@@ -1619,19 +1619,19 @@
         <v>29.67</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2.64</v>
+        <v>2.12</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>3.44</v>
+        <v>2.92</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>3.59</v>
+        <v>3.07</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>9.130000000000001</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
@@ -1697,19 +1697,19 @@
         <v>33.9</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>4.44</v>
+        <v>3.55</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>3.74</v>
+        <v>3.22</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>8.18</v>
+        <v>6.77</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>8.33</v>
+        <v>6.92</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>9.130000000000001</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
@@ -1775,19 +1775,19 @@
         <v>36.21</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1.99</v>
+        <v>1.59</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>2.59</v>
+        <v>2.19</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>2.74</v>
+        <v>2.34</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>11</v>
+        <v>14.11</v>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
@@ -1853,19 +1853,19 @@
         <v>39.95</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3.94</v>
+        <v>3.16</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>4.54</v>
+        <v>3.76</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>4.69</v>
+        <v>3.91</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
@@ -1931,19 +1931,19 @@
         <v>2.5</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>11.47</v>
+        <v>14.69</v>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
@@ -2009,19 +2009,19 @@
         <v>5.21</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2.72</v>
+        <v>2.19</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>3.9</v>
+        <v>7.35</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>6.61</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>6.76</v>
+        <v>9.69</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>11.47</v>
+        <v>14.69</v>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
@@ -2087,19 +2087,19 @@
         <v>8.640000000000001</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>6.91</v>
+        <v>9.84</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>10.52</v>
+        <v>12.74</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>10.67</v>
+        <v>12.89</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>11.47</v>
+        <v>14.69</v>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
@@ -2165,19 +2165,19 @@
         <v>11.94</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>3.5</v>
+        <v>2.82</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>5.45</v>
+        <v>4.64</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>8.949999999999999</v>
+        <v>7.46</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>9.1</v>
+        <v>7.61</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>13.02</v>
+        <v>11.98</v>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
@@ -2243,19 +2243,19 @@
         <v>14.79</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2.82</v>
+        <v>2.27</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>9.25</v>
+        <v>7.76</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>12.07</v>
+        <v>10.03</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>12.22</v>
+        <v>10.18</v>
       </c>
       <c r="Q23" s="2" t="n">
-        <v>13.02</v>
+        <v>11.98</v>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
@@ -2321,19 +2321,19 @@
         <v>20.14</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>6.22</v>
+        <v>4.99</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>5.89</v>
+        <v>6</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>12.11</v>
+        <v>10.99</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>12.26</v>
+        <v>11.14</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>13.06</v>
+        <v>12.94</v>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
@@ -2399,19 +2399,19 @@
         <v>23.88</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>3.76</v>
+        <v>3</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>4.69</v>
+        <v>4.04</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>8.449999999999999</v>
+        <v>7.04</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>8.6</v>
+        <v>7.19</v>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
@@ -2477,19 +2477,19 @@
         <v>27.35</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>3.66</v>
+        <v>2.93</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>3.86</v>
+        <v>3.36</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>7.51</v>
+        <v>6.28</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>7.66</v>
+        <v>6.43</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.23</v>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
@@ -2555,19 +2555,19 @@
         <v>4.06</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>4.78</v>
+        <v>3.84</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>3.59</v>
+        <v>3.18</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>8.369999999999999</v>
+        <v>7.02</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>8.52</v>
+        <v>7.17</v>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>9.32</v>
+        <v>9</v>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
@@ -2633,19 +2633,19 @@
         <v>7.63</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>3.92</v>
+        <v>3.16</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>8.109999999999999</v>
+        <v>6.81</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>8.26</v>
+        <v>6.96</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>9.06</v>
+        <v>9</v>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
@@ -2711,19 +2711,19 @@
         <v>11.56</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>4.05</v>
+        <v>3.27</v>
       </c>
       <c r="N29" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>4.85</v>
+        <v>4.07</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>5</v>
+        <v>4.22</v>
       </c>
       <c r="Q29" s="2" t="n">
-        <v>21.56</v>
+        <v>20.98</v>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
@@ -2789,19 +2789,19 @@
         <v>16.91</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>5.51</v>
+        <v>4.41</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>5.15</v>
+        <v>5.37</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>10.66</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>10.81</v>
+        <v>9.93</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>21.56</v>
+        <v>20.98</v>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
@@ -2867,19 +2867,19 @@
         <v>21.43</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>4.73</v>
+        <v>3.79</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>4.77</v>
+        <v>4.12</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>9.5</v>
+        <v>7.9</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>9.65</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Q31" s="2" t="n">
-        <v>17.42</v>
+        <v>16.57</v>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
@@ -2945,19 +2945,19 @@
         <v>26.38</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>5.12</v>
+        <v>4.1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>4.95</v>
+        <v>4.27</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>10.07</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>10.22</v>
+        <v>8.52</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>17.34</v>
+        <v>15.52</v>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
@@ -3023,19 +3023,19 @@
         <v>31.87</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>6.14</v>
+        <v>4.94</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>5.14</v>
+        <v>5.4</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>11.27</v>
+        <v>10.34</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>11.42</v>
+        <v>10.49</v>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>20.18</v>
+        <v>19.86</v>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
@@ -3101,19 +3101,19 @@
         <v>34.96</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3.06</v>
+        <v>2.46</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>3.67</v>
+        <v>3.23</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>6.73</v>
+        <v>5.68</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>6.88</v>
+        <v>5.83</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
@@ -3139,12 +3139,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>先輩のヒント</t>
+          <t>問い</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>hint-P1-Q1</t>
+          <t>q-P1-Q1</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -3179,19 +3179,19 @@
         <v>6.93</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>8.41</v>
+        <v>6.74</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.6</v>
+        <v>3.13</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>9.01</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>9.16</v>
+        <v>10.02</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>9.960000000000001</v>
+        <v>16.82</v>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
@@ -3217,12 +3217,12 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>先輩のヒント</t>
+          <t>問い</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>hint-P1-Q2</t>
+          <t>q-P1-Q2</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -3257,19 +3257,19 @@
         <v>13.74</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>8.18</v>
+        <v>6.58</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.6</v>
+        <v>4.44</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>8.779999999999999</v>
+        <v>11.02</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>8.93</v>
+        <v>11.17</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>9.73</v>
+        <v>17.97</v>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
@@ -3295,12 +3295,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>先輩のヒント</t>
+          <t>問い</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>hint-P3-Q1</t>
+          <t>q-P3-Q1</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -3335,19 +3335,19 @@
         <v>18.43</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>5.43</v>
+        <v>4.36</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.6</v>
+        <v>2.79</v>
       </c>
       <c r="O37" s="2" t="n">
-        <v>6.03</v>
+        <v>7.16</v>
       </c>
       <c r="P37" s="2" t="n">
-        <v>6.18</v>
+        <v>7.31</v>
       </c>
       <c r="Q37" s="2" t="n">
-        <v>6.98</v>
+        <v>14.11</v>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
@@ -3413,19 +3413,19 @@
         <v>24.39</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>6.97</v>
+        <v>5.59</v>
       </c>
       <c r="N38" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>7.57</v>
+        <v>6.19</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>7.72</v>
+        <v>6.34</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>8.52</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
@@ -3491,19 +3491,19 @@
         <v>29.23</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>4.99</v>
+        <v>4</v>
       </c>
       <c r="N39" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>5.79</v>
+        <v>4.8</v>
       </c>
       <c r="P39" s="2" t="n">
-        <v>5.94</v>
+        <v>4.95</v>
       </c>
       <c r="Q39" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
@@ -3529,12 +3529,12 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>先輩のヒント</t>
+          <t>問い</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>hint-P4-Q1</t>
+          <t>q-P4-Q1</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3569,19 +3569,19 @@
         <v>34.07</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>5.22</v>
+        <v>4.21</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.6</v>
+        <v>4.44</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>5.82</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>5.97</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>6.77</v>
+        <v>15.59</v>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
@@ -3647,19 +3647,19 @@
         <v>38.94</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>5.56</v>
+        <v>4.47</v>
       </c>
       <c r="N41" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>6.36</v>
+        <v>5.27</v>
       </c>
       <c r="P41" s="2" t="n">
-        <v>6.51</v>
+        <v>5.42</v>
       </c>
       <c r="Q41" s="2" t="n">
-        <v>20.95</v>
+        <v>19.27</v>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
@@ -3725,19 +3725,19 @@
         <v>43.71</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>5.67</v>
+        <v>4.55</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>6.66</v>
+        <v>6.57</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>12.33</v>
+        <v>11.11</v>
       </c>
       <c r="P42" s="2" t="n">
-        <v>12.48</v>
+        <v>11.26</v>
       </c>
       <c r="Q42" s="2" t="n">
-        <v>20.95</v>
+        <v>19.27</v>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
@@ -3803,19 +3803,19 @@
         <v>50.32</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>7.37</v>
+        <v>5.9</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>12.63</v>
+        <v>11.41</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>20</v>
+        <v>17.32</v>
       </c>
       <c r="P43" s="2" t="n">
-        <v>20.15</v>
+        <v>17.47</v>
       </c>
       <c r="Q43" s="2" t="n">
-        <v>20.95</v>
+        <v>19.27</v>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
@@ -3881,19 +3881,19 @@
         <v>57.37</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>8.119999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="N44" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>8.92</v>
+        <v>7.3</v>
       </c>
       <c r="P44" s="2" t="n">
-        <v>9.07</v>
+        <v>7.45</v>
       </c>
       <c r="Q44" s="2" t="n">
-        <v>25.23</v>
+        <v>21.84</v>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
@@ -3919,12 +3919,12 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>先輩のヒント</t>
+          <t>問い</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>hint-P4-Q3</t>
+          <t>q-P4-Q3</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -3959,19 +3959,19 @@
         <v>61.81</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>4.91</v>
+        <v>3.94</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.6</v>
+        <v>5.38</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>5.51</v>
+        <v>9.32</v>
       </c>
       <c r="P45" s="2" t="n">
-        <v>5.66</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="Q45" s="2" t="n">
-        <v>6.46</v>
+        <v>16.27</v>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
@@ -4037,19 +4037,19 @@
         <v>3.45</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>4.05</v>
+        <v>3.24</v>
       </c>
       <c r="N46" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O46" s="2" t="n">
-        <v>4.85</v>
+        <v>4.04</v>
       </c>
       <c r="P46" s="2" t="n">
-        <v>5</v>
+        <v>4.19</v>
       </c>
       <c r="Q46" s="2" t="n">
-        <v>13.02</v>
+        <v>11.98</v>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
@@ -4115,19 +4115,19 @@
         <v>7.56</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>4.49</v>
+        <v>3.6</v>
       </c>
       <c r="N47" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O47" s="2" t="n">
-        <v>5.29</v>
+        <v>4.4</v>
       </c>
       <c r="P47" s="2" t="n">
-        <v>5.44</v>
+        <v>4.55</v>
       </c>
       <c r="Q47" s="2" t="n">
-        <v>13.06</v>
+        <v>12.94</v>
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
@@ -4193,19 +4193,19 @@
         <v>10.67</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>3.29</v>
+        <v>2.64</v>
       </c>
       <c r="N48" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O48" s="2" t="n">
-        <v>4.09</v>
+        <v>3.44</v>
       </c>
       <c r="P48" s="2" t="n">
-        <v>4.24</v>
+        <v>3.59</v>
       </c>
       <c r="Q48" s="2" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
@@ -4271,19 +4271,19 @@
         <v>13.1</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2.46</v>
+        <v>1.96</v>
       </c>
       <c r="N49" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O49" s="2" t="n">
-        <v>3.26</v>
+        <v>2.76</v>
       </c>
       <c r="P49" s="2" t="n">
-        <v>3.41</v>
+        <v>2.91</v>
       </c>
       <c r="Q49" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.23</v>
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
@@ -4349,19 +4349,19 @@
         <v>15.27</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>2.19</v>
+        <v>1.78</v>
       </c>
       <c r="N50" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O50" s="2" t="n">
-        <v>2.99</v>
+        <v>2.58</v>
       </c>
       <c r="P50" s="2" t="n">
-        <v>3.14</v>
+        <v>2.73</v>
       </c>
       <c r="Q50" s="2" t="n">
-        <v>9.32</v>
+        <v>9</v>
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
@@ -4427,19 +4427,19 @@
         <v>17.91</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="N51" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O51" s="2" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="P51" s="2" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="Q51" s="2" t="n">
-        <v>9.06</v>
+        <v>9</v>
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
@@ -4505,19 +4505,19 @@
         <v>21.08</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>3.37</v>
+        <v>2.72</v>
       </c>
       <c r="N52" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O52" s="2" t="n">
-        <v>4.17</v>
+        <v>3.52</v>
       </c>
       <c r="P52" s="2" t="n">
-        <v>4.32</v>
+        <v>3.67</v>
       </c>
       <c r="Q52" s="2" t="n">
-        <v>17.42</v>
+        <v>16.57</v>
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
@@ -4583,19 +4583,19 @@
         <v>24.37</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>3.55</v>
+        <v>2.87</v>
       </c>
       <c r="N53" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O53" s="2" t="n">
-        <v>4.35</v>
+        <v>3.67</v>
       </c>
       <c r="P53" s="2" t="n">
-        <v>4.5</v>
+        <v>3.82</v>
       </c>
       <c r="Q53" s="2" t="n">
-        <v>17.34</v>
+        <v>15.52</v>
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
@@ -4661,19 +4661,19 @@
         <v>27.83</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>3.74</v>
+        <v>3</v>
       </c>
       <c r="N54" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O54" s="2" t="n">
-        <v>4.54</v>
+        <v>3.8</v>
       </c>
       <c r="P54" s="2" t="n">
-        <v>4.69</v>
+        <v>3.95</v>
       </c>
       <c r="Q54" s="2" t="n">
-        <v>20.18</v>
+        <v>19.86</v>
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
@@ -4739,19 +4739,19 @@
         <v>31.22</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>3.74</v>
+        <v>3</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>13.26</v>
+        <v>11.04</v>
       </c>
       <c r="O55" s="2" t="n">
-        <v>16.99</v>
+        <v>14.04</v>
       </c>
       <c r="P55" s="2" t="n">
-        <v>17.14</v>
+        <v>14.19</v>
       </c>
       <c r="Q55" s="2" t="n">
-        <v>30.85</v>
+        <v>26.6</v>
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
@@ -4817,19 +4817,19 @@
         <v>2.05</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2.27</v>
+        <v>1.83</v>
       </c>
       <c r="N56" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O56" s="2" t="n">
-        <v>3.07</v>
+        <v>2.63</v>
       </c>
       <c r="P56" s="2" t="n">
-        <v>3.22</v>
+        <v>2.78</v>
       </c>
       <c r="Q56" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
@@ -4895,19 +4895,19 @@
         <v>8.68</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>7.26</v>
+        <v>5.8</v>
       </c>
       <c r="N57" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>8.06</v>
+        <v>6.6</v>
       </c>
       <c r="P57" s="2" t="n">
-        <v>8.210000000000001</v>
+        <v>6.75</v>
       </c>
       <c r="Q57" s="2" t="n">
-        <v>21.3</v>
+        <v>18.7</v>
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
@@ -4973,19 +4973,19 @@
         <v>11.17</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2.19</v>
+        <v>1.78</v>
       </c>
       <c r="N58" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O58" s="2" t="n">
-        <v>2.99</v>
+        <v>2.58</v>
       </c>
       <c r="P58" s="2" t="n">
-        <v>3.14</v>
+        <v>2.73</v>
       </c>
       <c r="Q58" s="2" t="n">
-        <v>8.359999999999999</v>
+        <v>9</v>
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
@@ -5051,19 +5051,19 @@
         <v>15.72</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>4.81</v>
+        <v>3.87</v>
       </c>
       <c r="N59" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O59" s="2" t="n">
-        <v>5.61</v>
+        <v>4.67</v>
       </c>
       <c r="P59" s="2" t="n">
-        <v>5.76</v>
+        <v>4.82</v>
       </c>
       <c r="Q59" s="2" t="n">
-        <v>15.08</v>
+        <v>13.65</v>
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
@@ -5129,19 +5129,19 @@
         <v>18.33</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>2.59</v>
+        <v>2.09</v>
       </c>
       <c r="N60" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O60" s="2" t="n">
-        <v>3.39</v>
+        <v>2.89</v>
       </c>
       <c r="P60" s="2" t="n">
-        <v>3.54</v>
+        <v>3.04</v>
       </c>
       <c r="Q60" s="2" t="n">
-        <v>9.01</v>
+        <v>9</v>
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
@@ -5207,19 +5207,19 @@
         <v>21.68</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>3.42</v>
+        <v>2.77</v>
       </c>
       <c r="N61" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O61" s="2" t="n">
-        <v>4.22</v>
+        <v>3.57</v>
       </c>
       <c r="P61" s="2" t="n">
-        <v>4.37</v>
+        <v>3.72</v>
       </c>
       <c r="Q61" s="2" t="n">
-        <v>10.47</v>
+        <v>9.91</v>
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
@@ -5285,19 +5285,19 @@
         <v>25.71</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>4.15</v>
+        <v>3.34</v>
       </c>
       <c r="N62" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O62" s="2" t="n">
-        <v>4.95</v>
+        <v>4.14</v>
       </c>
       <c r="P62" s="2" t="n">
-        <v>5.1</v>
+        <v>4.29</v>
       </c>
       <c r="Q62" s="2" t="n">
-        <v>9.85</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
@@ -5363,19 +5363,19 @@
         <v>31.76</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>6.64</v>
+        <v>5.33</v>
       </c>
       <c r="N63" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O63" s="2" t="n">
-        <v>7.44</v>
+        <v>6.13</v>
       </c>
       <c r="P63" s="2" t="n">
-        <v>7.59</v>
+        <v>6.28</v>
       </c>
       <c r="Q63" s="2" t="n">
-        <v>15.74</v>
+        <v>14.18</v>
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
@@ -5441,19 +5441,19 @@
         <v>4.76</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>5.64</v>
+        <v>4.52</v>
       </c>
       <c r="N64" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O64" s="2" t="n">
-        <v>6.44</v>
+        <v>5.32</v>
       </c>
       <c r="P64" s="2" t="n">
-        <v>6.59</v>
+        <v>5.47</v>
       </c>
       <c r="Q64" s="2" t="n">
-        <v>21.29</v>
+        <v>18.53</v>
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
@@ -5519,19 +5519,19 @@
         <v>11.33</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>7.44</v>
+        <v>5.98</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>6.74</v>
+        <v>5.62</v>
       </c>
       <c r="O65" s="2" t="n">
-        <v>14.19</v>
+        <v>11.6</v>
       </c>
       <c r="P65" s="2" t="n">
-        <v>14.34</v>
+        <v>11.75</v>
       </c>
       <c r="Q65" s="2" t="n">
-        <v>21.29</v>
+        <v>18.53</v>
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
@@ -5597,19 +5597,19 @@
         <v>16.53</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>5.85</v>
+        <v>4.68</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>14.49</v>
+        <v>11.9</v>
       </c>
       <c r="O66" s="2" t="n">
-        <v>20.34</v>
+        <v>16.58</v>
       </c>
       <c r="P66" s="2" t="n">
-        <v>20.49</v>
+        <v>16.73</v>
       </c>
       <c r="Q66" s="2" t="n">
-        <v>21.29</v>
+        <v>18.53</v>
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
@@ -5675,19 +5675,19 @@
         <v>20.72</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>4.44</v>
+        <v>3.55</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>5.16</v>
+        <v>4.4</v>
       </c>
       <c r="O67" s="2" t="n">
-        <v>9.6</v>
+        <v>7.96</v>
       </c>
       <c r="P67" s="2" t="n">
-        <v>9.75</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="Q67" s="2" t="n">
-        <v>10.55</v>
+        <v>9.91</v>
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
@@ -5753,19 +5753,19 @@
         <v>24.4</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>4</v>
+        <v>3.21</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>6.21</v>
+        <v>5.27</v>
       </c>
       <c r="O68" s="2" t="n">
-        <v>10.2</v>
+        <v>8.48</v>
       </c>
       <c r="P68" s="2" t="n">
-        <v>10.35</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="Q68" s="2" t="n">
-        <v>15.08</v>
+        <v>13.65</v>
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
@@ -5831,19 +5831,19 @@
         <v>27.72</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>3.63</v>
+        <v>2.93</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>10.5</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="O69" s="2" t="n">
-        <v>14.13</v>
+        <v>11.7</v>
       </c>
       <c r="P69" s="2" t="n">
-        <v>14.28</v>
+        <v>11.85</v>
       </c>
       <c r="Q69" s="2" t="n">
-        <v>15.08</v>
+        <v>13.65</v>
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
@@ -5909,19 +5909,19 @@
         <v>31.86</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>4.7</v>
+        <v>3.79</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>4.82</v>
+        <v>4.17</v>
       </c>
       <c r="O70" s="2" t="n">
-        <v>9.52</v>
+        <v>7.96</v>
       </c>
       <c r="P70" s="2" t="n">
-        <v>9.67</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="Q70" s="2" t="n">
-        <v>10.47</v>
+        <v>9.91</v>
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
@@ -5987,19 +5987,19 @@
         <v>34.92</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>3.55</v>
+        <v>2.87</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>4.4</v>
+        <v>3.83</v>
       </c>
       <c r="O71" s="2" t="n">
-        <v>7.96</v>
+        <v>6.7</v>
       </c>
       <c r="P71" s="2" t="n">
-        <v>8.109999999999999</v>
+        <v>6.85</v>
       </c>
       <c r="Q71" s="2" t="n">
-        <v>8.91</v>
+        <v>9</v>
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
@@ -6065,19 +6065,19 @@
         <v>37.68</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2.95</v>
+        <v>2.35</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>4.95</v>
+        <v>4.25</v>
       </c>
       <c r="O72" s="2" t="n">
-        <v>7.9</v>
+        <v>6.6</v>
       </c>
       <c r="P72" s="2" t="n">
-        <v>8.050000000000001</v>
+        <v>6.75</v>
       </c>
       <c r="Q72" s="2" t="n">
-        <v>8.85</v>
+        <v>9</v>
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
@@ -6143,19 +6143,19 @@
         <v>41.37</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>4.05</v>
+        <v>3.27</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>4.43</v>
+        <v>3.86</v>
       </c>
       <c r="O73" s="2" t="n">
-        <v>8.48</v>
+        <v>7.12</v>
       </c>
       <c r="P73" s="2" t="n">
-        <v>8.630000000000001</v>
+        <v>7.27</v>
       </c>
       <c r="Q73" s="2" t="n">
-        <v>9.43</v>
+        <v>9.07</v>
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
@@ -6221,19 +6221,19 @@
         <v>2.6</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2.98</v>
+        <v>2.4</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>11.26</v>
+        <v>11.38</v>
       </c>
       <c r="O74" s="2" t="n">
-        <v>14.24</v>
+        <v>13.78</v>
       </c>
       <c r="P74" s="2" t="n">
-        <v>14.39</v>
+        <v>13.93</v>
       </c>
       <c r="Q74" s="2" t="n">
-        <v>21.56</v>
+        <v>20.98</v>
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
@@ -6299,19 +6299,19 @@
         <v>5.53</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>3.06</v>
+        <v>2.46</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>14.54</v>
+        <v>14.08</v>
       </c>
       <c r="O75" s="2" t="n">
-        <v>17.6</v>
+        <v>16.54</v>
       </c>
       <c r="P75" s="2" t="n">
-        <v>17.75</v>
+        <v>16.69</v>
       </c>
       <c r="Q75" s="2" t="n">
-        <v>21.56</v>
+        <v>20.98</v>
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
@@ -6377,19 +6377,19 @@
         <v>8.109999999999999</v>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2.72</v>
+        <v>2.19</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>17.9</v>
+        <v>16.84</v>
       </c>
       <c r="O76" s="2" t="n">
-        <v>20.61</v>
+        <v>19.03</v>
       </c>
       <c r="P76" s="2" t="n">
-        <v>20.76</v>
+        <v>19.18</v>
       </c>
       <c r="Q76" s="2" t="n">
-        <v>21.56</v>
+        <v>20.98</v>
       </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
@@ -6455,19 +6455,19 @@
         <v>16.05</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>7.39</v>
       </c>
       <c r="N77" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O77" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>7.99</v>
       </c>
       <c r="P77" s="2" t="n">
-        <v>9.949999999999999</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="Q77" s="2" t="n">
-        <v>10.75</v>
+        <v>9.94</v>
       </c>
       <c r="R77" s="2" t="inlineStr">
         <is>
@@ -6533,19 +6533,19 @@
         <v>21.88</v>
       </c>
       <c r="M78" s="2" t="n">
-        <v>6.37</v>
+        <v>5.12</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>10.1</v>
+        <v>9.5</v>
       </c>
       <c r="O78" s="2" t="n">
-        <v>16.47</v>
+        <v>14.62</v>
       </c>
       <c r="P78" s="2" t="n">
-        <v>16.62</v>
+        <v>14.77</v>
       </c>
       <c r="Q78" s="2" t="n">
-        <v>17.42</v>
+        <v>16.57</v>
       </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
@@ -6611,19 +6611,19 @@
         <v>26.85</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>5.72</v>
+        <v>4.6</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>10.67</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="O79" s="2" t="n">
-        <v>16.39</v>
+        <v>13.57</v>
       </c>
       <c r="P79" s="2" t="n">
-        <v>16.54</v>
+        <v>13.72</v>
       </c>
       <c r="Q79" s="2" t="n">
-        <v>17.34</v>
+        <v>15.52</v>
       </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
@@ -6689,19 +6689,19 @@
         <v>30.35</v>
       </c>
       <c r="M80" s="2" t="n">
-        <v>3.66</v>
+        <v>2.93</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>11.87</v>
+        <v>10.94</v>
       </c>
       <c r="O80" s="2" t="n">
-        <v>15.53</v>
+        <v>13.87</v>
       </c>
       <c r="P80" s="2" t="n">
-        <v>15.68</v>
+        <v>14.02</v>
       </c>
       <c r="Q80" s="2" t="n">
-        <v>20.18</v>
+        <v>19.86</v>
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
@@ -6767,19 +6767,19 @@
         <v>33.39</v>
       </c>
       <c r="M81" s="2" t="n">
-        <v>3.4</v>
+        <v>2.74</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>15.83</v>
+        <v>15.17</v>
       </c>
       <c r="O81" s="2" t="n">
-        <v>19.23</v>
+        <v>17.91</v>
       </c>
       <c r="P81" s="2" t="n">
-        <v>19.38</v>
+        <v>18.06</v>
       </c>
       <c r="Q81" s="2" t="n">
-        <v>20.18</v>
+        <v>19.86</v>
       </c>
       <c r="R81" s="2" t="inlineStr">
         <is>
@@ -6845,19 +6845,19 @@
         <v>3.5</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>4.1</v>
+        <v>3.32</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>8.56</v>
+        <v>7.12</v>
       </c>
       <c r="O82" s="2" t="n">
-        <v>12.66</v>
+        <v>10.44</v>
       </c>
       <c r="P82" s="2" t="n">
-        <v>12.81</v>
+        <v>10.59</v>
       </c>
       <c r="Q82" s="2" t="n">
-        <v>30.85</v>
+        <v>26.6</v>
       </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
@@ -6923,19 +6923,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>6.74</v>
+        <v>5.41</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>17.59</v>
+        <v>14.64</v>
       </c>
       <c r="O83" s="2" t="n">
-        <v>24.33</v>
+        <v>20.05</v>
       </c>
       <c r="P83" s="2" t="n">
-        <v>24.48</v>
+        <v>20.2</v>
       </c>
       <c r="Q83" s="2" t="n">
-        <v>30.85</v>
+        <v>26.6</v>
       </c>
       <c r="R83" s="2" t="inlineStr">
         <is>
@@ -6961,12 +6961,12 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>先輩のヒント</t>
+          <t>問い</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>hint-P2-Q2</t>
+          <t>q-P2-Q2</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -7001,19 +7001,19 @@
         <v>13.97</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>4.13</v>
+        <v>3.32</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.6</v>
+        <v>3.05</v>
       </c>
       <c r="O84" s="2" t="n">
-        <v>4.73</v>
+        <v>6.37</v>
       </c>
       <c r="P84" s="2" t="n">
-        <v>4.88</v>
+        <v>6.52</v>
       </c>
       <c r="Q84" s="2" t="n">
-        <v>5.68</v>
+        <v>13.32</v>
       </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
@@ -7079,19 +7079,19 @@
         <v>17.71</v>
       </c>
       <c r="M85" s="2" t="n">
-        <v>3.84</v>
+        <v>3.08</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>12.81</v>
+        <v>10.62</v>
       </c>
       <c r="O85" s="2" t="n">
-        <v>16.65</v>
+        <v>13.7</v>
       </c>
       <c r="P85" s="2" t="n">
-        <v>16.8</v>
+        <v>13.85</v>
       </c>
       <c r="Q85" s="2" t="n">
-        <v>21.3</v>
+        <v>18.7</v>
       </c>
       <c r="R85" s="2" t="inlineStr">
         <is>
@@ -7157,19 +7157,19 @@
         <v>21.01</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>3.4</v>
+        <v>2.74</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>16.95</v>
+        <v>14</v>
       </c>
       <c r="O86" s="2" t="n">
-        <v>20.35</v>
+        <v>16.75</v>
       </c>
       <c r="P86" s="2" t="n">
-        <v>20.5</v>
+        <v>16.9</v>
       </c>
       <c r="Q86" s="2" t="n">
-        <v>21.3</v>
+        <v>18.7</v>
       </c>
       <c r="R86" s="2" t="inlineStr">
         <is>
@@ -7235,19 +7235,19 @@
         <v>27.32</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>7.13</v>
+        <v>5.72</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>11.61</v>
+        <v>9.58</v>
       </c>
       <c r="O87" s="2" t="n">
-        <v>18.75</v>
+        <v>15.3</v>
       </c>
       <c r="P87" s="2" t="n">
-        <v>18.9</v>
+        <v>15.45</v>
       </c>
       <c r="Q87" s="2" t="n">
-        <v>25.1</v>
+        <v>21.71</v>
       </c>
       <c r="R87" s="2" t="inlineStr">
         <is>
@@ -7313,19 +7313,19 @@
         <v>31.76</v>
       </c>
       <c r="M88" s="2" t="n">
-        <v>4.83</v>
+        <v>3.89</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>9.52</v>
+        <v>7.9</v>
       </c>
       <c r="O88" s="2" t="n">
-        <v>14.36</v>
+        <v>11.8</v>
       </c>
       <c r="P88" s="2" t="n">
-        <v>14.51</v>
+        <v>11.95</v>
       </c>
       <c r="Q88" s="2" t="n">
-        <v>25.23</v>
+        <v>21.84</v>
       </c>
       <c r="R88" s="2" t="inlineStr">
         <is>
@@ -7391,19 +7391,19 @@
         <v>3.12</v>
       </c>
       <c r="M89" s="2" t="n">
-        <v>3.55</v>
+        <v>2.82</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>8.66</v>
+        <v>7.2</v>
       </c>
       <c r="O89" s="2" t="n">
-        <v>12.21</v>
+        <v>10.02</v>
       </c>
       <c r="P89" s="2" t="n">
-        <v>12.36</v>
+        <v>10.17</v>
       </c>
       <c r="Q89" s="2" t="n">
-        <v>21.3</v>
+        <v>18.7</v>
       </c>
       <c r="R89" s="2" t="inlineStr">
         <is>
@@ -7469,19 +7469,19 @@
         <v>6.79</v>
       </c>
       <c r="M90" s="2" t="n">
-        <v>3.81</v>
+        <v>3.08</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>3.59</v>
+        <v>3.18</v>
       </c>
       <c r="O90" s="2" t="n">
-        <v>7.41</v>
+        <v>6.26</v>
       </c>
       <c r="P90" s="2" t="n">
-        <v>7.56</v>
+        <v>6.41</v>
       </c>
       <c r="Q90" s="2" t="n">
-        <v>8.359999999999999</v>
+        <v>9</v>
       </c>
       <c r="R90" s="2" t="inlineStr">
         <is>
@@ -7547,19 +7547,19 @@
         <v>10.43</v>
       </c>
       <c r="M91" s="2" t="n">
-        <v>3.76</v>
+        <v>3</v>
       </c>
       <c r="N91" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O91" s="2" t="n">
-        <v>4.56</v>
+        <v>3.8</v>
       </c>
       <c r="P91" s="2" t="n">
-        <v>4.71</v>
+        <v>3.95</v>
       </c>
       <c r="Q91" s="2" t="n">
-        <v>10.55</v>
+        <v>9.91</v>
       </c>
       <c r="R91" s="2" t="inlineStr">
         <is>
@@ -7625,19 +7625,19 @@
         <v>14.4</v>
       </c>
       <c r="M92" s="2" t="n">
-        <v>4.08</v>
+        <v>3.27</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>3.99</v>
+        <v>3.49</v>
       </c>
       <c r="O92" s="2" t="n">
-        <v>8.06</v>
+        <v>6.76</v>
       </c>
       <c r="P92" s="2" t="n">
-        <v>8.210000000000001</v>
+        <v>6.91</v>
       </c>
       <c r="Q92" s="2" t="n">
-        <v>9.01</v>
+        <v>9</v>
       </c>
       <c r="R92" s="2" t="inlineStr">
         <is>
@@ -7703,19 +7703,19 @@
         <v>17.76</v>
       </c>
       <c r="M93" s="2" t="n">
-        <v>3.34</v>
+        <v>2.69</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>5.55</v>
+        <v>4.74</v>
       </c>
       <c r="O93" s="2" t="n">
-        <v>8.9</v>
+        <v>7.43</v>
       </c>
       <c r="P93" s="2" t="n">
-        <v>9.050000000000001</v>
+        <v>7.58</v>
       </c>
       <c r="Q93" s="2" t="n">
-        <v>9.85</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="R93" s="2" t="inlineStr">
         <is>
@@ -7781,19 +7781,19 @@
         <v>19.35</v>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>8.039999999999999</v>
+        <v>6.73</v>
       </c>
       <c r="O94" s="2" t="n">
-        <v>9.289999999999999</v>
+        <v>7.75</v>
       </c>
       <c r="P94" s="2" t="n">
-        <v>9.44</v>
+        <v>7.9</v>
       </c>
       <c r="Q94" s="2" t="n">
-        <v>15.74</v>
+        <v>14.18</v>
       </c>
       <c r="R94" s="2" t="inlineStr">
         <is>
@@ -7859,19 +7859,19 @@
         <v>24.08</v>
       </c>
       <c r="M95" s="2" t="n">
-        <v>5.2</v>
+        <v>4.18</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>9.59</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O95" s="2" t="n">
-        <v>14.79</v>
+        <v>12.23</v>
       </c>
       <c r="P95" s="2" t="n">
-        <v>14.94</v>
+        <v>12.38</v>
       </c>
       <c r="Q95" s="2" t="n">
-        <v>15.74</v>
+        <v>14.18</v>
       </c>
       <c r="R95" s="2" t="inlineStr">
         <is>
@@ -7937,19 +7937,19 @@
         <v>28.77</v>
       </c>
       <c r="M96" s="2" t="n">
-        <v>5.15</v>
+        <v>4.13</v>
       </c>
       <c r="N96" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O96" s="2" t="n">
-        <v>5.95</v>
+        <v>4.93</v>
       </c>
       <c r="P96" s="2" t="n">
-        <v>6.1</v>
+        <v>5.08</v>
       </c>
       <c r="Q96" s="2" t="n">
-        <v>18.64</v>
+        <v>17.48</v>
       </c>
       <c r="R96" s="2" t="inlineStr">
         <is>
@@ -8015,19 +8015,19 @@
         <v>32.92</v>
       </c>
       <c r="M97" s="2" t="n">
-        <v>4.52</v>
+        <v>3.63</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>5.55</v>
+        <v>4.74</v>
       </c>
       <c r="O97" s="2" t="n">
-        <v>10.07</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="P97" s="2" t="n">
-        <v>10.22</v>
+        <v>8.52</v>
       </c>
       <c r="Q97" s="2" t="n">
-        <v>11.02</v>
+        <v>10.32</v>
       </c>
       <c r="R97" s="2" t="inlineStr">
         <is>
@@ -8093,19 +8093,19 @@
         <v>37.77</v>
       </c>
       <c r="M98" s="2" t="n">
-        <v>5.36</v>
+        <v>4.31</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>7.04</v>
+        <v>5.95</v>
       </c>
       <c r="O98" s="2" t="n">
-        <v>12.4</v>
+        <v>10.26</v>
       </c>
       <c r="P98" s="2" t="n">
-        <v>12.55</v>
+        <v>10.41</v>
       </c>
       <c r="Q98" s="2" t="n">
-        <v>13.35</v>
+        <v>12.21</v>
       </c>
       <c r="R98" s="2" t="inlineStr">
         <is>
@@ -8171,19 +8171,19 @@
         <v>41.65</v>
       </c>
       <c r="M99" s="2" t="n">
-        <v>4.13</v>
+        <v>3.32</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>5.08</v>
+        <v>4.38</v>
       </c>
       <c r="O99" s="2" t="n">
-        <v>9.210000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="P99" s="2" t="n">
-        <v>9.359999999999999</v>
+        <v>7.85</v>
       </c>
       <c r="Q99" s="2" t="n">
-        <v>10.16</v>
+        <v>9.65</v>
       </c>
       <c r="R99" s="2" t="inlineStr">
         <is>
@@ -8249,19 +8249,19 @@
         <v>45.15</v>
       </c>
       <c r="M100" s="2" t="n">
-        <v>3.66</v>
+        <v>2.93</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>7.64</v>
+        <v>6.42</v>
       </c>
       <c r="O100" s="2" t="n">
-        <v>11.3</v>
+        <v>9.34</v>
       </c>
       <c r="P100" s="2" t="n">
-        <v>11.45</v>
+        <v>9.49</v>
       </c>
       <c r="Q100" s="2" t="n">
-        <v>14.33</v>
+        <v>13.03</v>
       </c>
       <c r="R100" s="2" t="inlineStr">
         <is>
@@ -8327,19 +8327,19 @@
         <v>47.08</v>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1.78</v>
+        <v>1.44</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>11.6</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="O101" s="2" t="n">
-        <v>13.38</v>
+        <v>11.08</v>
       </c>
       <c r="P101" s="2" t="n">
-        <v>13.53</v>
+        <v>11.23</v>
       </c>
       <c r="Q101" s="2" t="n">
-        <v>14.33</v>
+        <v>13.03</v>
       </c>
       <c r="R101" s="2" t="inlineStr">
         <is>
@@ -8405,19 +8405,19 @@
         <v>50.22</v>
       </c>
       <c r="M102" s="2" t="n">
-        <v>3.27</v>
+        <v>2.64</v>
       </c>
       <c r="N102" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O102" s="2" t="n">
-        <v>4.07</v>
+        <v>3.44</v>
       </c>
       <c r="P102" s="2" t="n">
-        <v>4.22</v>
+        <v>3.59</v>
       </c>
       <c r="Q102" s="2" t="n">
-        <v>15.21</v>
+        <v>13.76</v>
       </c>
       <c r="R102" s="2" t="inlineStr">
         <is>
@@ -8483,19 +8483,19 @@
         <v>54.17</v>
       </c>
       <c r="M103" s="2" t="n">
-        <v>4.21</v>
+        <v>3.37</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>4.37</v>
+        <v>3.74</v>
       </c>
       <c r="O103" s="2" t="n">
-        <v>8.57</v>
+        <v>7.11</v>
       </c>
       <c r="P103" s="2" t="n">
-        <v>8.720000000000001</v>
+        <v>7.26</v>
       </c>
       <c r="Q103" s="2" t="n">
-        <v>15.21</v>
+        <v>13.76</v>
       </c>
       <c r="R103" s="2" t="inlineStr">
         <is>
@@ -8561,19 +8561,19 @@
         <v>2.6</v>
       </c>
       <c r="M104" s="2" t="n">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="N104" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O104" s="2" t="n">
-        <v>3.8</v>
+        <v>3.23</v>
       </c>
       <c r="P104" s="2" t="n">
-        <v>3.95</v>
+        <v>3.38</v>
       </c>
       <c r="Q104" s="2" t="n">
-        <v>8.91</v>
+        <v>9</v>
       </c>
       <c r="R104" s="2" t="inlineStr">
         <is>
@@ -8639,19 +8639,19 @@
         <v>6.63</v>
       </c>
       <c r="M105" s="2" t="n">
-        <v>4.15</v>
+        <v>3.34</v>
       </c>
       <c r="N105" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O105" s="2" t="n">
-        <v>4.95</v>
+        <v>4.14</v>
       </c>
       <c r="P105" s="2" t="n">
-        <v>5.1</v>
+        <v>4.29</v>
       </c>
       <c r="Q105" s="2" t="n">
-        <v>11.02</v>
+        <v>10.32</v>
       </c>
       <c r="R105" s="2" t="inlineStr">
         <is>
@@ -8717,19 +8717,19 @@
         <v>12.02</v>
       </c>
       <c r="M106" s="2" t="n">
-        <v>5.64</v>
+        <v>4.55</v>
       </c>
       <c r="N106" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O106" s="2" t="n">
-        <v>6.44</v>
+        <v>5.35</v>
       </c>
       <c r="P106" s="2" t="n">
-        <v>6.59</v>
+        <v>5.5</v>
       </c>
       <c r="Q106" s="2" t="n">
-        <v>13.35</v>
+        <v>12.21</v>
       </c>
       <c r="R106" s="2" t="inlineStr">
         <is>
@@ -8795,19 +8795,19 @@
         <v>15.51</v>
       </c>
       <c r="M107" s="2" t="n">
-        <v>3.55</v>
+        <v>2.85</v>
       </c>
       <c r="N107" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O107" s="2" t="n">
-        <v>4.35</v>
+        <v>3.65</v>
       </c>
       <c r="P107" s="2" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q107" s="2" t="n">
-        <v>8.85</v>
+        <v>9</v>
       </c>
       <c r="R107" s="2" t="inlineStr">
         <is>
@@ -8873,19 +8873,19 @@
         <v>19.24</v>
       </c>
       <c r="M108" s="2" t="n">
-        <v>3.68</v>
+        <v>2.98</v>
       </c>
       <c r="N108" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O108" s="2" t="n">
-        <v>4.48</v>
+        <v>3.78</v>
       </c>
       <c r="P108" s="2" t="n">
-        <v>4.63</v>
+        <v>3.93</v>
       </c>
       <c r="Q108" s="2" t="n">
-        <v>10.16</v>
+        <v>9.65</v>
       </c>
       <c r="R108" s="2" t="inlineStr">
         <is>
@@ -8951,19 +8951,19 @@
         <v>24.95</v>
       </c>
       <c r="M109" s="2" t="n">
-        <v>6.24</v>
+        <v>5.02</v>
       </c>
       <c r="N109" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O109" s="2" t="n">
-        <v>7.04</v>
+        <v>5.82</v>
       </c>
       <c r="P109" s="2" t="n">
-        <v>7.19</v>
+        <v>5.97</v>
       </c>
       <c r="Q109" s="2" t="n">
-        <v>14.33</v>
+        <v>13.03</v>
       </c>
       <c r="R109" s="2" t="inlineStr">
         <is>
@@ -9029,19 +9029,19 @@
         <v>28.05</v>
       </c>
       <c r="M110" s="2" t="n">
-        <v>3.03</v>
+        <v>2.46</v>
       </c>
       <c r="N110" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O110" s="2" t="n">
-        <v>3.83</v>
+        <v>3.26</v>
       </c>
       <c r="P110" s="2" t="n">
-        <v>3.98</v>
+        <v>3.41</v>
       </c>
       <c r="Q110" s="2" t="n">
-        <v>9.43</v>
+        <v>9.07</v>
       </c>
       <c r="R110" s="2" t="inlineStr">
         <is>
@@ -9107,19 +9107,19 @@
         <v>5.7</v>
       </c>
       <c r="M111" s="2" t="n">
-        <v>6.82</v>
+        <v>5.46</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>6.55</v>
+        <v>6.53</v>
       </c>
       <c r="O111" s="2" t="n">
-        <v>13.36</v>
+        <v>11.99</v>
       </c>
       <c r="P111" s="2" t="n">
-        <v>13.51</v>
+        <v>12.14</v>
       </c>
       <c r="Q111" s="2" t="n">
-        <v>18.64</v>
+        <v>17.48</v>
       </c>
       <c r="R111" s="2" t="inlineStr">
         <is>
@@ -9185,19 +9185,19 @@
         <v>9.19</v>
       </c>
       <c r="M112" s="2" t="n">
-        <v>4.02</v>
+        <v>3.24</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>13.66</v>
+        <v>12.29</v>
       </c>
       <c r="O112" s="2" t="n">
-        <v>17.69</v>
+        <v>15.53</v>
       </c>
       <c r="P112" s="2" t="n">
-        <v>17.84</v>
+        <v>15.68</v>
       </c>
       <c r="Q112" s="2" t="n">
-        <v>18.64</v>
+        <v>17.48</v>
       </c>
       <c r="R112" s="2" t="inlineStr">
         <is>
@@ -9263,19 +9263,19 @@
         <v>11.89</v>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2.61</v>
+        <v>2.12</v>
       </c>
       <c r="N113" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O113" s="2" t="n">
-        <v>3.41</v>
+        <v>2.92</v>
       </c>
       <c r="P113" s="2" t="n">
-        <v>3.56</v>
+        <v>3.07</v>
       </c>
       <c r="Q113" s="2" t="n">
-        <v>8.74</v>
+        <v>8.43</v>
       </c>
       <c r="R113" s="2" t="inlineStr">
         <is>
@@ -9341,19 +9341,19 @@
         <v>15.39</v>
       </c>
       <c r="M114" s="2" t="n">
-        <v>4.08</v>
+        <v>3.27</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>3.71</v>
+        <v>3.22</v>
       </c>
       <c r="O114" s="2" t="n">
-        <v>7.79</v>
+        <v>6.48</v>
       </c>
       <c r="P114" s="2" t="n">
-        <v>7.94</v>
+        <v>6.63</v>
       </c>
       <c r="Q114" s="2" t="n">
-        <v>8.74</v>
+        <v>8.43</v>
       </c>
       <c r="R114" s="2" t="inlineStr">
         <is>
@@ -9419,19 +9419,19 @@
         <v>19.59</v>
       </c>
       <c r="M115" s="2" t="n">
-        <v>4.02</v>
+        <v>3.24</v>
       </c>
       <c r="N115" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O115" s="2" t="n">
-        <v>4.62</v>
+        <v>3.84</v>
       </c>
       <c r="P115" s="2" t="n">
-        <v>4.77</v>
+        <v>3.99</v>
       </c>
       <c r="Q115" s="2" t="n">
-        <v>11</v>
+        <v>15.59</v>
       </c>
       <c r="R115" s="2" t="inlineStr">
         <is>
@@ -9497,19 +9497,19 @@
         <v>24.07</v>
       </c>
       <c r="M116" s="2" t="n">
-        <v>4.75</v>
+        <v>3.81</v>
       </c>
       <c r="N116" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O116" s="2" t="n">
-        <v>5.55</v>
+        <v>4.61</v>
       </c>
       <c r="P116" s="2" t="n">
-        <v>5.7</v>
+        <v>4.76</v>
       </c>
       <c r="Q116" s="2" t="n">
-        <v>18.86</v>
+        <v>16.62</v>
       </c>
       <c r="R116" s="2" t="inlineStr">
         <is>
@@ -9575,19 +9575,19 @@
         <v>29.56</v>
       </c>
       <c r="M117" s="2" t="n">
-        <v>6.79</v>
+        <v>5.46</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>5.85</v>
+        <v>4.91</v>
       </c>
       <c r="O117" s="2" t="n">
-        <v>12.65</v>
+        <v>10.37</v>
       </c>
       <c r="P117" s="2" t="n">
-        <v>12.8</v>
+        <v>10.52</v>
       </c>
       <c r="Q117" s="2" t="n">
-        <v>18.86</v>
+        <v>16.62</v>
       </c>
       <c r="R117" s="2" t="inlineStr">
         <is>
@@ -9653,19 +9653,19 @@
         <v>33.6</v>
       </c>
       <c r="M118" s="2" t="n">
-        <v>4.96</v>
+        <v>4</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>12.95</v>
+        <v>10.67</v>
       </c>
       <c r="O118" s="2" t="n">
-        <v>17.91</v>
+        <v>14.67</v>
       </c>
       <c r="P118" s="2" t="n">
-        <v>18.06</v>
+        <v>14.82</v>
       </c>
       <c r="Q118" s="2" t="n">
-        <v>18.86</v>
+        <v>16.62</v>
       </c>
       <c r="R118" s="2" t="inlineStr">
         <is>
@@ -9731,19 +9731,19 @@
         <v>38.05</v>
       </c>
       <c r="M119" s="2" t="n">
-        <v>5.2</v>
+        <v>4.18</v>
       </c>
       <c r="N119" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O119" s="2" t="n">
-        <v>5.8</v>
+        <v>4.78</v>
       </c>
       <c r="P119" s="2" t="n">
-        <v>5.95</v>
+        <v>4.93</v>
       </c>
       <c r="Q119" s="2" t="n">
-        <v>11.75</v>
+        <v>16.27</v>
       </c>
       <c r="R119" s="2" t="inlineStr">
         <is>
@@ -9809,19 +9809,19 @@
         <v>3.43</v>
       </c>
       <c r="M120" s="2" t="n">
-        <v>4.05</v>
+        <v>3.27</v>
       </c>
       <c r="N120" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O120" s="2" t="n">
-        <v>4.85</v>
+        <v>4.07</v>
       </c>
       <c r="P120" s="2" t="n">
-        <v>5</v>
+        <v>4.22</v>
       </c>
       <c r="Q120" s="2" t="n">
-        <v>22.99</v>
+        <v>19.89</v>
       </c>
       <c r="R120" s="2" t="inlineStr">
         <is>
@@ -9887,19 +9887,19 @@
         <v>12.39</v>
       </c>
       <c r="M121" s="2" t="n">
-        <v>10.42</v>
+        <v>8.33</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>5.15</v>
+        <v>4.37</v>
       </c>
       <c r="O121" s="2" t="n">
-        <v>15.57</v>
+        <v>12.7</v>
       </c>
       <c r="P121" s="2" t="n">
-        <v>15.72</v>
+        <v>12.85</v>
       </c>
       <c r="Q121" s="2" t="n">
-        <v>22.99</v>
+        <v>19.89</v>
       </c>
       <c r="R121" s="2" t="inlineStr">
         <is>
@@ -9965,19 +9965,19 @@
         <v>18.2</v>
       </c>
       <c r="M122" s="2" t="n">
-        <v>6.16</v>
+        <v>4.94</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>15.87</v>
+        <v>13</v>
       </c>
       <c r="O122" s="2" t="n">
-        <v>22.04</v>
+        <v>17.94</v>
       </c>
       <c r="P122" s="2" t="n">
-        <v>22.19</v>
+        <v>18.09</v>
       </c>
       <c r="Q122" s="2" t="n">
-        <v>22.99</v>
+        <v>19.89</v>
       </c>
       <c r="R122" s="2" t="inlineStr">
         <is>
@@ -10043,19 +10043,19 @@
         <v>23.17</v>
       </c>
       <c r="M123" s="2" t="n">
-        <v>5.09</v>
+        <v>4.1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>9.17</v>
+        <v>7.71</v>
       </c>
       <c r="O123" s="2" t="n">
-        <v>14.26</v>
+        <v>11.81</v>
       </c>
       <c r="P123" s="2" t="n">
-        <v>14.41</v>
+        <v>11.96</v>
       </c>
       <c r="Q123" s="2" t="n">
-        <v>15.21</v>
+        <v>13.76</v>
       </c>
       <c r="R123" s="2" t="inlineStr">
         <is>
@@ -10121,19 +10121,19 @@
         <v>29.04</v>
       </c>
       <c r="M124" s="2" t="n">
-        <v>6.32</v>
+        <v>5.07</v>
       </c>
       <c r="N124" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O124" s="2" t="n">
-        <v>7.12</v>
+        <v>5.87</v>
       </c>
       <c r="P124" s="2" t="n">
-        <v>7.27</v>
+        <v>6.02</v>
       </c>
       <c r="Q124" s="2" t="n">
-        <v>8.07</v>
+        <v>7.82</v>
       </c>
       <c r="R124" s="2" t="inlineStr">
         <is>
@@ -10199,19 +10199,19 @@
         <v>31.81</v>
       </c>
       <c r="M125" s="2" t="n">
-        <v>2.59</v>
+        <v>2.06</v>
       </c>
       <c r="N125" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O125" s="2" t="n">
-        <v>3.19</v>
+        <v>2.66</v>
       </c>
       <c r="P125" s="2" t="n">
-        <v>3.34</v>
+        <v>2.81</v>
       </c>
       <c r="Q125" s="2" t="n">
-        <v>4.14</v>
+        <v>5</v>
       </c>
       <c r="R125" s="2" t="inlineStr">
         <is>
@@ -10277,19 +10277,19 @@
         <v>35.63</v>
       </c>
       <c r="M126" s="2" t="n">
-        <v>4.05</v>
+        <v>3.24</v>
       </c>
       <c r="N126" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O126" s="2" t="n">
-        <v>4.65</v>
+        <v>3.84</v>
       </c>
       <c r="P126" s="2" t="n">
-        <v>4.8</v>
+        <v>3.99</v>
       </c>
       <c r="Q126" s="2" t="n">
-        <v>5.6</v>
+        <v>5.79</v>
       </c>
       <c r="R126" s="2" t="inlineStr">
         <is>
@@ -10355,19 +10355,19 @@
         <v>2.66</v>
       </c>
       <c r="M127" s="2" t="n">
-        <v>3.06</v>
+        <v>2.48</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>14.66</v>
+        <v>12.1</v>
       </c>
       <c r="O127" s="2" t="n">
-        <v>17.71</v>
+        <v>14.58</v>
       </c>
       <c r="P127" s="2" t="n">
-        <v>17.86</v>
+        <v>14.73</v>
       </c>
       <c r="Q127" s="2" t="n">
-        <v>25.23</v>
+        <v>21.84</v>
       </c>
       <c r="R127" s="2" t="inlineStr">
         <is>
@@ -10433,19 +10433,19 @@
         <v>8</v>
       </c>
       <c r="M128" s="2" t="n">
-        <v>6.27</v>
+        <v>5.02</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>18.01</v>
+        <v>14.88</v>
       </c>
       <c r="O128" s="2" t="n">
-        <v>24.28</v>
+        <v>19.89</v>
       </c>
       <c r="P128" s="2" t="n">
-        <v>24.43</v>
+        <v>20.04</v>
       </c>
       <c r="Q128" s="2" t="n">
-        <v>25.23</v>
+        <v>21.84</v>
       </c>
       <c r="R128" s="2" t="inlineStr">
         <is>
@@ -10511,19 +10511,19 @@
         <v>12.43</v>
       </c>
       <c r="M129" s="2" t="n">
-        <v>4.88</v>
+        <v>3.92</v>
       </c>
       <c r="N129" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O129" s="2" t="n">
-        <v>5.68</v>
+        <v>4.72</v>
       </c>
       <c r="P129" s="2" t="n">
-        <v>5.83</v>
+        <v>4.87</v>
       </c>
       <c r="Q129" s="2" t="n">
-        <v>26.06</v>
+        <v>22.41</v>
       </c>
       <c r="R129" s="2" t="inlineStr">
         <is>
@@ -10589,19 +10589,19 @@
         <v>17.72</v>
       </c>
       <c r="M130" s="2" t="n">
-        <v>6.14</v>
+        <v>4.91</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>5.98</v>
+        <v>5.02</v>
       </c>
       <c r="O130" s="2" t="n">
-        <v>12.12</v>
+        <v>9.93</v>
       </c>
       <c r="P130" s="2" t="n">
-        <v>12.27</v>
+        <v>10.08</v>
       </c>
       <c r="Q130" s="2" t="n">
-        <v>26.06</v>
+        <v>22.41</v>
       </c>
       <c r="R130" s="2" t="inlineStr">
         <is>
@@ -10667,19 +10667,19 @@
         <v>21.57</v>
       </c>
       <c r="M131" s="2" t="n">
-        <v>4.34</v>
+        <v>3.47</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>12.42</v>
+        <v>10.23</v>
       </c>
       <c r="O131" s="2" t="n">
-        <v>16.76</v>
+        <v>13.7</v>
       </c>
       <c r="P131" s="2" t="n">
-        <v>16.91</v>
+        <v>13.85</v>
       </c>
       <c r="Q131" s="2" t="n">
-        <v>26.06</v>
+        <v>22.41</v>
       </c>
       <c r="R131" s="2" t="inlineStr">
         <is>
@@ -10745,19 +10745,19 @@
         <v>28.42</v>
       </c>
       <c r="M132" s="2" t="n">
-        <v>8.050000000000001</v>
+        <v>6.45</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>17.06</v>
+        <v>14</v>
       </c>
       <c r="O132" s="2" t="n">
-        <v>25.11</v>
+        <v>20.46</v>
       </c>
       <c r="P132" s="2" t="n">
-        <v>25.26</v>
+        <v>20.61</v>
       </c>
       <c r="Q132" s="2" t="n">
-        <v>26.06</v>
+        <v>22.41</v>
       </c>
       <c r="R132" s="2" t="inlineStr">
         <is>
@@ -10823,19 +10823,19 @@
         <v>2.78</v>
       </c>
       <c r="M133" s="2" t="n">
-        <v>3.16</v>
+        <v>2.56</v>
       </c>
       <c r="N133" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O133" s="2" t="n">
-        <v>3.76</v>
+        <v>3.16</v>
       </c>
       <c r="P133" s="2" t="n">
-        <v>3.91</v>
+        <v>3.31</v>
       </c>
       <c r="Q133" s="2" t="n">
-        <v>4.71</v>
+        <v>5.11</v>
       </c>
       <c r="R133" s="2" t="inlineStr">
         <is>
@@ -10901,19 +10901,19 @@
         <v>6.11</v>
       </c>
       <c r="M134" s="2" t="n">
-        <v>3.29</v>
+        <v>2.64</v>
       </c>
       <c r="N134" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="O134" s="2" t="n">
-        <v>3.89</v>
+        <v>3.24</v>
       </c>
       <c r="P134" s="2" t="n">
-        <v>4.04</v>
+        <v>3.39</v>
       </c>
       <c r="Q134" s="2" t="n">
-        <v>4.84</v>
+        <v>5.19</v>
       </c>
       <c r="R134" s="2" t="inlineStr">
         <is>
@@ -10979,19 +10979,19 @@
         <v>10.61</v>
       </c>
       <c r="M135" s="2" t="n">
-        <v>3.92</v>
+        <v>3.13</v>
       </c>
       <c r="N135" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="O135" s="2" t="n">
-        <v>4.72</v>
+        <v>3.93</v>
       </c>
       <c r="P135" s="2" t="n">
-        <v>4.87</v>
+        <v>4.08</v>
       </c>
       <c r="Q135" s="2" t="n">
-        <v>22.19</v>
+        <v>19.32</v>
       </c>
       <c r="R135" s="2" t="inlineStr">
         <is>
@@ -11057,19 +11057,19 @@
         <v>16.76</v>
       </c>
       <c r="M136" s="2" t="n">
-        <v>6.95</v>
+        <v>5.56</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>5.02</v>
+        <v>4.23</v>
       </c>
       <c r="O136" s="2" t="n">
-        <v>11.97</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="P136" s="2" t="n">
-        <v>12.12</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q136" s="2" t="n">
-        <v>22.19</v>
+        <v>19.32</v>
       </c>
       <c r="R136" s="2" t="inlineStr">
         <is>
@@ -11135,19 +11135,19 @@
         <v>20.59</v>
       </c>
       <c r="M137" s="2" t="n">
-        <v>4</v>
+        <v>3.21</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>12.27</v>
+        <v>10.1</v>
       </c>
       <c r="O137" s="2" t="n">
-        <v>16.26</v>
+        <v>13.31</v>
       </c>
       <c r="P137" s="2" t="n">
-        <v>16.41</v>
+        <v>13.46</v>
       </c>
       <c r="Q137" s="2" t="n">
-        <v>22.19</v>
+        <v>19.32</v>
       </c>
       <c r="R137" s="2" t="inlineStr">
         <is>
@@ -11213,19 +11213,19 @@
         <v>24.79</v>
       </c>
       <c r="M138" s="2" t="n">
-        <v>4.68</v>
+        <v>3.76</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>16.56</v>
+        <v>13.61</v>
       </c>
       <c r="O138" s="2" t="n">
-        <v>21.24</v>
+        <v>17.37</v>
       </c>
       <c r="P138" s="2" t="n">
-        <v>21.39</v>
+        <v>17.52</v>
       </c>
       <c r="Q138" s="2" t="n">
-        <v>22.19</v>
+        <v>19.32</v>
       </c>
       <c r="R138" s="2" t="inlineStr">
         <is>
